--- a/facturador_template.xlsx
+++ b/facturador_template.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
   <si>
     <t>Cliente</t>
   </si>
@@ -47,19 +47,40 @@
     <t>Realizado</t>
   </si>
   <si>
+    <t>Pto Venta</t>
+  </si>
+  <si>
+    <t>Cod. Actividad</t>
+  </si>
+  <si>
     <t>RI</t>
   </si>
   <si>
-    <t>27/12/2024</t>
+    <t>20/03/2026</t>
   </si>
   <si>
-    <t>Diciembre 2024</t>
+    <t>Marzo 2026</t>
+  </si>
+  <si>
+    <t>✓</t>
+  </si>
+  <si>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>M</t>
   </si>
   <si>
     <t>ZUCCHET PIETRO EZIO</t>
   </si>
   <si>
-    <t>31/12/2024</t>
+    <t>Juan Rodriguez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empresa SRL </t>
+  </si>
+  <si>
+    <t>Fernando Goméz</t>
   </si>
 </sst>
 </file>
@@ -70,7 +91,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* \-??\ _€_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="mmm/yy"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -120,6 +141,19 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -255,7 +289,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -280,26 +314,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -316,54 +335,88 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -820,21 +873,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR108"/>
+  <dimension ref="A1:BR74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.375" style="4" customWidth="1"/>
     <col min="3" max="3" width="13.25" style="4" customWidth="1"/>
-    <col min="4" max="4" width="13.5" style="19" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="19" customWidth="1"/>
-    <col min="6" max="6" width="12.75" style="20" customWidth="1"/>
+    <col min="4" max="4" width="13.5" style="12" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="12" customWidth="1"/>
+    <col min="6" max="6" width="12.75" style="13" customWidth="1"/>
     <col min="7" max="7" width="13.25" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.75" style="6" customWidth="1"/>
     <col min="9" max="9" width="13.125" style="6" customWidth="1"/>
-    <col min="10" max="38" width="11.375" style="6" customWidth="1"/>
-    <col min="39" max="67" width="11.375" style="2" customWidth="1"/>
-    <col min="68" max="16384" width="11.375" style="2"/>
+    <col min="10" max="10" width="11.375" style="6" customWidth="1"/>
+    <col min="11" max="11" width="11.375" style="39" customWidth="1"/>
+    <col min="12" max="38" width="11.375" style="6" customWidth="1"/>
+    <col min="39" max="102" width="11.375" style="2" customWidth="1"/>
+    <col min="103" max="16384" width="11.375" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:70" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -847,26 +902,32 @@
       <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="14" t="s">
         <v>9</v>
+      </c>
+      <c r="K1" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="36" t="s">
+        <v>11</v>
       </c>
       <c r="AM1" s="2"/>
       <c r="AN1" s="2"/>
@@ -906,26 +967,44 @@
       </c>
     </row>
     <row r="2" spans="1:70" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="22">
+      <c r="A2" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="41">
+        <v>2025454669</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="8">
+        <v>76000</v>
+      </c>
+      <c r="E2" s="15">
         <f t="shared" ref="E2:E33" si="0">+D2*0.21</f>
-        <v>0</v>
-      </c>
-      <c r="F2" s="23">
+        <v>15960</v>
+      </c>
+      <c r="F2" s="16">
         <f t="shared" ref="F2:F33" si="1">+E2+D2</f>
-        <v>0</v>
-      </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="15"/>
+        <v>91960</v>
+      </c>
+      <c r="G2" s="45">
+        <v>16445</v>
+      </c>
+      <c r="H2" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="49">
+        <v>2</v>
+      </c>
+      <c r="L2" s="49">
+        <v>681098</v>
+      </c>
       <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
@@ -958,26 +1037,44 @@
       <c r="BP2" s="2"/>
     </row>
     <row r="3" spans="1:70" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="22">
+      <c r="A3" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="41">
+        <v>3070885789</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="42">
+        <v>53223.03</v>
+      </c>
+      <c r="E3" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F3" s="23">
+        <v>11176.836299999999</v>
+      </c>
+      <c r="F3" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="15"/>
+        <v>64399.866299999994</v>
+      </c>
+      <c r="G3" s="9">
+        <v>16403</v>
+      </c>
+      <c r="H3" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="49">
+        <v>2</v>
+      </c>
+      <c r="L3" s="49">
+        <v>681098</v>
+      </c>
       <c r="AM3" s="2"/>
       <c r="AN3" s="2"/>
       <c r="AO3" s="2"/>
@@ -1010,28 +1107,44 @@
       <c r="BP3" s="2"/>
     </row>
     <row r="4" spans="1:70" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F4" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
+      <c r="A4" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="41">
+        <v>2030265112</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="8">
+        <v>14080</v>
+      </c>
+      <c r="E4" s="15">
+        <f t="shared" ref="E4" si="2">+D4*0.21</f>
+        <v>2956.7999999999997</v>
+      </c>
+      <c r="F4" s="16">
+        <f t="shared" ref="F4" si="3">+E4+D4</f>
+        <v>17036.8</v>
+      </c>
+      <c r="G4" s="9">
+        <v>16404</v>
+      </c>
+      <c r="H4" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="49">
+        <v>2</v>
+      </c>
+      <c r="L4" s="49">
+        <v>681098</v>
+      </c>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
@@ -1090,28 +1203,18 @@
       <c r="BP4" s="2"/>
     </row>
     <row r="5" spans="1:70" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="26"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F5" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="14"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
+      <c r="A5" s="40"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
@@ -1170,28 +1273,18 @@
       <c r="BP5" s="2"/>
     </row>
     <row r="6" spans="1:70" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F6" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="A6" s="40"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="14"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
@@ -1250,30 +1343,20 @@
       <c r="BP6" s="2"/>
     </row>
     <row r="7" spans="1:70" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="29"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="A7" s="40"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="14"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="49"/>
       <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
+      <c r="N7" s="41"/>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
@@ -1330,28 +1413,18 @@
       <c r="BP7" s="2"/>
     </row>
     <row r="8" spans="1:70" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="29"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="A8" s="40"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="8"/>
-      <c r="E8" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F8" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
       <c r="G8" s="9"/>
-      <c r="H8" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J8" s="14"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="47"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
@@ -1410,28 +1483,18 @@
       <c r="BP8" s="2"/>
     </row>
     <row r="9" spans="1:70" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="29"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J9" s="14"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
+      <c r="A9" s="40"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="49"/>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
@@ -1490,28 +1553,18 @@
       <c r="BP9" s="2"/>
     </row>
     <row r="10" spans="1:70" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J10" s="14"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
+      <c r="A10" s="40"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
@@ -1570,28 +1623,18 @@
       <c r="BP10" s="2"/>
     </row>
     <row r="11" spans="1:70" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F11" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J11" s="14"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
+      <c r="A11" s="40"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="49"/>
+      <c r="L11" s="49"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
@@ -1650,28 +1693,18 @@
       <c r="BP11" s="2"/>
     </row>
     <row r="12" spans="1:70" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="32"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F12" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="E12" s="15"/>
+      <c r="F12" s="16"/>
       <c r="G12" s="9"/>
-      <c r="H12" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J12" s="14"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="49"/>
+      <c r="L12" s="49"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
@@ -1730,28 +1763,18 @@
       <c r="BP12" s="2"/>
     </row>
     <row r="13" spans="1:70" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="29"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="E13" s="15"/>
+      <c r="F13" s="16"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" s="14"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="49"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
@@ -1810,28 +1833,18 @@
       <c r="BP13" s="2"/>
     </row>
     <row r="14" spans="1:70" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="29"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="E14" s="15"/>
+      <c r="F14" s="16"/>
       <c r="G14" s="9"/>
-      <c r="H14" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J14" s="14"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="49"/>
+      <c r="L14" s="49"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
@@ -1890,28 +1903,18 @@
       <c r="BP14" s="2"/>
     </row>
     <row r="15" spans="1:70" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="29"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
+      <c r="A15" s="40"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F15" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="E15" s="15"/>
+      <c r="F15" s="16"/>
       <c r="G15" s="9"/>
-      <c r="H15" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J15" s="14"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="49"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
       <c r="O15" s="6"/>
@@ -1970,28 +1973,18 @@
       <c r="BP15" s="2"/>
     </row>
     <row r="16" spans="1:70" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="29"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
+      <c r="A16" s="40"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="E16" s="15"/>
+      <c r="F16" s="16"/>
       <c r="G16" s="9"/>
-      <c r="H16" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J16" s="14"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="48"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="49"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
@@ -2050,28 +2043,24 @@
       <c r="BP16" s="2"/>
     </row>
     <row r="17" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
+      <c r="A17" s="19"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="30"/>
+      <c r="C17" s="20"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="22">
+      <c r="E17" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G17" s="9"/>
-      <c r="H17" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J17" s="14"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37"/>
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
@@ -2130,28 +2119,24 @@
       <c r="BP17" s="2"/>
     </row>
     <row r="18" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
+      <c r="A18" s="19"/>
       <c r="B18" s="1"/>
-      <c r="C18" s="30"/>
+      <c r="C18" s="1"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="22">
+      <c r="E18" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G18" s="9"/>
-      <c r="H18" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J18" s="14"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="37"/>
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
@@ -2212,26 +2197,22 @@
     <row r="19" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
+      <c r="C19" s="20"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="22">
+      <c r="E19" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G19" s="9"/>
-      <c r="H19" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J19" s="14"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
@@ -2290,28 +2271,24 @@
       <c r="BP19" s="2"/>
     </row>
     <row r="20" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="29"/>
+      <c r="A20" s="3"/>
       <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
+      <c r="C20" s="20"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="22">
+      <c r="E20" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G20" s="9"/>
-      <c r="H20" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J20" s="14"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="37"/>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
@@ -2370,28 +2347,24 @@
       <c r="BP20" s="2"/>
     </row>
     <row r="21" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="29"/>
+      <c r="A21" s="3"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
+      <c r="C21" s="20"/>
       <c r="D21" s="8"/>
-      <c r="E21" s="22">
+      <c r="E21" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G21" s="9"/>
-      <c r="H21" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J21" s="14"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="37"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
       <c r="O21" s="6"/>
@@ -2450,28 +2423,24 @@
       <c r="BP21" s="2"/>
     </row>
     <row r="22" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="29"/>
+      <c r="A22" s="19"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="8"/>
-      <c r="E22" s="22">
+      <c r="E22" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G22" s="9"/>
-      <c r="H22" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J22" s="14"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="37"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
       <c r="O22" s="6"/>
@@ -2532,26 +2501,22 @@
     <row r="23" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
+      <c r="C23" s="20"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="22">
+      <c r="E23" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G23" s="9"/>
-      <c r="H23" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J23" s="14"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
       <c r="O23" s="6"/>
@@ -2611,27 +2576,23 @@
     </row>
     <row r="24" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
       <c r="D24" s="8"/>
-      <c r="E24" s="22">
+      <c r="E24" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G24" s="9"/>
-      <c r="H24" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J24" s="14"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="37"/>
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
       <c r="O24" s="6"/>
@@ -2690,28 +2651,24 @@
       <c r="BP24" s="2"/>
     </row>
     <row r="25" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
+      <c r="A25" s="19"/>
       <c r="B25" s="1"/>
-      <c r="C25" s="30"/>
+      <c r="C25" s="1"/>
       <c r="D25" s="8"/>
-      <c r="E25" s="22">
+      <c r="E25" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F25" s="23">
+      <c r="F25" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G25" s="9"/>
-      <c r="H25" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J25" s="14"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="37"/>
+      <c r="L25" s="37"/>
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
       <c r="O25" s="6"/>
@@ -2770,28 +2727,24 @@
       <c r="BP25" s="2"/>
     </row>
     <row r="26" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="29"/>
+      <c r="A26" s="19"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="8"/>
-      <c r="E26" s="22">
+      <c r="E26" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F26" s="23">
+      <c r="F26" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G26" s="9"/>
-      <c r="H26" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J26" s="14"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
       <c r="O26" s="6"/>
@@ -2850,28 +2803,24 @@
       <c r="BP26" s="2"/>
     </row>
     <row r="27" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
+      <c r="A27" s="19"/>
       <c r="B27" s="1"/>
-      <c r="C27" s="30"/>
+      <c r="C27" s="1"/>
       <c r="D27" s="8"/>
-      <c r="E27" s="22">
+      <c r="E27" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G27" s="9"/>
-      <c r="H27" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J27" s="14"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="38"/>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
       <c r="O27" s="6"/>
@@ -2930,28 +2879,24 @@
       <c r="BP27" s="2"/>
     </row>
     <row r="28" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="29"/>
+      <c r="A28" s="19"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="22">
+      <c r="E28" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F28" s="23">
+      <c r="F28" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G28" s="9"/>
-      <c r="H28" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J28" s="14"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="38"/>
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
@@ -3011,27 +2956,23 @@
     </row>
     <row r="29" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="29"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="32"/>
       <c r="D29" s="8"/>
-      <c r="E29" s="22">
+      <c r="E29" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F29" s="23">
+      <c r="F29" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G29" s="9"/>
-      <c r="H29" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J29" s="14"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="48"/>
+      <c r="K29" s="37"/>
+      <c r="L29" s="37"/>
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
       <c r="O29" s="6"/>
@@ -3090,28 +3031,24 @@
       <c r="BP29" s="2"/>
     </row>
     <row r="30" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3"/>
+      <c r="A30" s="19"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="8"/>
-      <c r="E30" s="22">
+      <c r="E30" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F30" s="23">
+      <c r="F30" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G30" s="9"/>
-      <c r="H30" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J30" s="14"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="47"/>
+      <c r="J30" s="48"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="37"/>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
       <c r="O30" s="6"/>
@@ -3170,28 +3107,24 @@
       <c r="BP30" s="2"/>
     </row>
     <row r="31" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="29"/>
+      <c r="A31" s="19"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="8"/>
-      <c r="E31" s="22">
+      <c r="E31" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F31" s="23">
+      <c r="F31" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G31" s="9"/>
-      <c r="H31" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I31" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J31" s="14"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="47"/>
+      <c r="J31" s="48"/>
+      <c r="K31" s="37"/>
+      <c r="L31" s="37"/>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
       <c r="O31" s="6"/>
@@ -3250,28 +3183,24 @@
       <c r="BP31" s="2"/>
     </row>
     <row r="32" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="29"/>
-      <c r="B32" s="33"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="8"/>
-      <c r="E32" s="22">
+      <c r="E32" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G32" s="9"/>
-      <c r="H32" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I32" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J32" s="14"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
+      <c r="H32" s="46"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="37"/>
+      <c r="L32" s="37"/>
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
       <c r="O32" s="6"/>
@@ -3331,27 +3260,23 @@
     </row>
     <row r="33" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
-      <c r="B33" s="1"/>
+      <c r="B33" s="20"/>
       <c r="C33" s="1"/>
       <c r="D33" s="8"/>
-      <c r="E33" s="22">
+      <c r="E33" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G33" s="9"/>
-      <c r="H33" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J33" s="14"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
+      <c r="H33" s="46"/>
+      <c r="I33" s="47"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="37"/>
+      <c r="L33" s="37"/>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
@@ -3410,28 +3335,24 @@
       <c r="BP33" s="2"/>
     </row>
     <row r="34" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="29"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
+      <c r="A34" s="3"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
       <c r="D34" s="8"/>
-      <c r="E34" s="22">
-        <f t="shared" ref="E34:E65" si="2">+D34*0.21</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="23">
-        <f t="shared" ref="F34:F65" si="3">+E34+D34</f>
+      <c r="E34" s="15">
+        <f t="shared" ref="E34:E65" si="4">+D34*0.21</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="16">
+        <f t="shared" ref="F34:F65" si="5">+E34+D34</f>
         <v>0</v>
       </c>
       <c r="G34" s="9"/>
-      <c r="H34" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I34" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J34" s="14"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
+      <c r="H34" s="46"/>
+      <c r="I34" s="47"/>
+      <c r="J34" s="48"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="37"/>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
       <c r="O34" s="6"/>
@@ -3490,28 +3411,24 @@
       <c r="BP34" s="2"/>
     </row>
     <row r="35" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="29"/>
+      <c r="A35" s="19"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="8"/>
-      <c r="E35" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F35" s="23">
-        <f t="shared" si="3"/>
+      <c r="E35" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G35" s="9"/>
-      <c r="H35" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I35" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J35" s="14"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
+      <c r="H35" s="46"/>
+      <c r="I35" s="47"/>
+      <c r="J35" s="48"/>
+      <c r="K35" s="37"/>
+      <c r="L35" s="37"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
       <c r="O35" s="6"/>
@@ -3570,28 +3487,24 @@
       <c r="BP35" s="2"/>
     </row>
     <row r="36" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="34"/>
-      <c r="B36" s="35"/>
-      <c r="C36" s="35"/>
+      <c r="A36" s="19"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
       <c r="D36" s="8"/>
-      <c r="E36" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F36" s="23">
-        <f t="shared" si="3"/>
+      <c r="E36" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G36" s="9"/>
-      <c r="H36" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I36" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J36" s="14"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="47"/>
+      <c r="J36" s="48"/>
+      <c r="K36" s="37"/>
+      <c r="L36" s="37"/>
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
@@ -3650,28 +3563,24 @@
       <c r="BP36" s="2"/>
     </row>
     <row r="37" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="29"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
+      <c r="A37" s="17"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
       <c r="D37" s="8"/>
-      <c r="E37" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F37" s="23">
-        <f t="shared" si="3"/>
+      <c r="E37" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G37" s="9"/>
-      <c r="H37" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I37" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J37" s="14"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
+      <c r="H37" s="46"/>
+      <c r="I37" s="47"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="37"/>
+      <c r="L37" s="37"/>
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
       <c r="O37" s="6"/>
@@ -3730,28 +3639,24 @@
       <c r="BP37" s="2"/>
     </row>
     <row r="38" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="26"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
       <c r="D38" s="8"/>
-      <c r="E38" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F38" s="23">
-        <f t="shared" si="3"/>
+      <c r="E38" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G38" s="9"/>
-      <c r="H38" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I38" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J38" s="14"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
+      <c r="H38" s="46"/>
+      <c r="I38" s="47"/>
+      <c r="J38" s="48"/>
+      <c r="K38" s="37"/>
+      <c r="L38" s="37"/>
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
       <c r="O38" s="6"/>
@@ -3810,28 +3715,24 @@
       <c r="BP38" s="2"/>
     </row>
     <row r="39" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="26"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
       <c r="D39" s="8"/>
-      <c r="E39" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F39" s="23">
-        <f t="shared" si="3"/>
+      <c r="E39" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G39" s="9"/>
-      <c r="H39" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I39" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J39" s="14"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
+      <c r="H39" s="46"/>
+      <c r="I39" s="47"/>
+      <c r="J39" s="48"/>
+      <c r="K39" s="37"/>
+      <c r="L39" s="37"/>
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
       <c r="O39" s="6"/>
@@ -3890,28 +3791,24 @@
       <c r="BP39" s="2"/>
     </row>
     <row r="40" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="36"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
+      <c r="A40" s="22"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="23"/>
       <c r="D40" s="8"/>
-      <c r="E40" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="23">
-        <f t="shared" si="3"/>
+      <c r="E40" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G40" s="9"/>
-      <c r="H40" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I40" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J40" s="14"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="6"/>
+      <c r="H40" s="46"/>
+      <c r="I40" s="47"/>
+      <c r="J40" s="48"/>
+      <c r="K40" s="37"/>
+      <c r="L40" s="37"/>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
       <c r="O40" s="6"/>
@@ -3970,28 +3867,24 @@
       <c r="BP40" s="2"/>
     </row>
     <row r="41" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="26"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
+      <c r="A41" s="22"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="23"/>
       <c r="D41" s="8"/>
-      <c r="E41" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F41" s="23">
-        <f t="shared" si="3"/>
+      <c r="E41" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G41" s="9"/>
-      <c r="H41" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I41" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J41" s="14"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
+      <c r="H41" s="46"/>
+      <c r="I41" s="47"/>
+      <c r="J41" s="48"/>
+      <c r="K41" s="37"/>
+      <c r="L41" s="37"/>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
       <c r="O41" s="6"/>
@@ -4050,28 +3943,24 @@
       <c r="BP41" s="2"/>
     </row>
     <row r="42" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="26"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
       <c r="D42" s="8"/>
-      <c r="E42" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F42" s="23">
-        <f t="shared" si="3"/>
+      <c r="E42" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G42" s="9"/>
-      <c r="H42" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I42" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J42" s="14"/>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6"/>
+      <c r="H42" s="46"/>
+      <c r="I42" s="47"/>
+      <c r="J42" s="48"/>
+      <c r="K42" s="37"/>
+      <c r="L42" s="37"/>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
       <c r="O42" s="6"/>
@@ -4130,28 +4019,24 @@
       <c r="BP42" s="2"/>
     </row>
     <row r="43" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="37"/>
-      <c r="B43" s="38"/>
-      <c r="C43" s="39"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
       <c r="D43" s="8"/>
-      <c r="E43" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F43" s="23">
-        <f t="shared" si="3"/>
+      <c r="E43" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G43" s="9"/>
-      <c r="H43" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I43" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J43" s="14"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
+      <c r="H43" s="46"/>
+      <c r="I43" s="47"/>
+      <c r="J43" s="48"/>
+      <c r="K43" s="37"/>
+      <c r="L43" s="37"/>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
       <c r="O43" s="6"/>
@@ -4210,28 +4095,24 @@
       <c r="BP43" s="2"/>
     </row>
     <row r="44" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="40"/>
-      <c r="B44" s="41"/>
-      <c r="C44" s="41"/>
+      <c r="A44" s="19"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="27"/>
       <c r="D44" s="8"/>
-      <c r="E44" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F44" s="23">
-        <f t="shared" si="3"/>
+      <c r="E44" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G44" s="9"/>
-      <c r="H44" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I44" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J44" s="14"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
+      <c r="H44" s="46"/>
+      <c r="I44" s="47"/>
+      <c r="J44" s="48"/>
+      <c r="K44" s="37"/>
+      <c r="L44" s="37"/>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
@@ -4290,28 +4171,24 @@
       <c r="BP44" s="2"/>
     </row>
     <row r="45" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="29"/>
+      <c r="A45" s="19"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="8"/>
-      <c r="E45" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F45" s="23">
-        <f t="shared" si="3"/>
+      <c r="E45" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G45" s="9"/>
-      <c r="H45" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I45" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J45" s="14"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
+      <c r="H45" s="46"/>
+      <c r="I45" s="47"/>
+      <c r="J45" s="48"/>
+      <c r="K45" s="37"/>
+      <c r="L45" s="37"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
       <c r="O45" s="6"/>
@@ -4370,28 +4247,24 @@
       <c r="BP45" s="2"/>
     </row>
     <row r="46" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
-      <c r="B46" s="31"/>
-      <c r="C46" s="42"/>
+      <c r="A46" s="19"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="18"/>
       <c r="D46" s="8"/>
-      <c r="E46" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F46" s="23">
-        <f t="shared" si="3"/>
+      <c r="E46" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F46" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G46" s="9"/>
-      <c r="H46" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I46" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J46" s="14"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="6"/>
+      <c r="H46" s="46"/>
+      <c r="I46" s="47"/>
+      <c r="J46" s="48"/>
+      <c r="K46" s="37"/>
+      <c r="L46" s="37"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
       <c r="O46" s="6"/>
@@ -4452,26 +4325,22 @@
     <row r="47" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="1"/>
-      <c r="C47" s="30"/>
+      <c r="C47" s="1"/>
       <c r="D47" s="8"/>
-      <c r="E47" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F47" s="23">
-        <f t="shared" si="3"/>
+      <c r="E47" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F47" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G47" s="9"/>
-      <c r="H47" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I47" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J47" s="14"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
+      <c r="H47" s="46"/>
+      <c r="I47" s="47"/>
+      <c r="J47" s="48"/>
+      <c r="K47" s="37"/>
+      <c r="L47" s="37"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
       <c r="O47" s="6"/>
@@ -4530,28 +4399,24 @@
       <c r="BP47" s="2"/>
     </row>
     <row r="48" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="29"/>
+      <c r="A48" s="19"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="8"/>
-      <c r="E48" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F48" s="23">
-        <f t="shared" si="3"/>
+      <c r="E48" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F48" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G48" s="9"/>
-      <c r="H48" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I48" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J48" s="14"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
+      <c r="H48" s="46"/>
+      <c r="I48" s="47"/>
+      <c r="J48" s="48"/>
+      <c r="K48" s="37"/>
+      <c r="L48" s="37"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
       <c r="O48" s="6"/>
@@ -4610,28 +4475,24 @@
       <c r="BP48" s="2"/>
     </row>
     <row r="49" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="29"/>
-      <c r="B49" s="1"/>
+      <c r="A49" s="19"/>
+      <c r="B49" s="21"/>
       <c r="C49" s="1"/>
       <c r="D49" s="8"/>
-      <c r="E49" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F49" s="23">
-        <f t="shared" si="3"/>
+      <c r="E49" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G49" s="9"/>
-      <c r="H49" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I49" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J49" s="14"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="6"/>
+      <c r="H49" s="46"/>
+      <c r="I49" s="47"/>
+      <c r="J49" s="48"/>
+      <c r="K49" s="37"/>
+      <c r="L49" s="37"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
       <c r="O49" s="6"/>
@@ -4692,26 +4553,22 @@
     <row r="50" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="1"/>
-      <c r="C50" s="30"/>
+      <c r="C50" s="1"/>
       <c r="D50" s="8"/>
-      <c r="E50" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F50" s="23">
-        <f t="shared" si="3"/>
+      <c r="E50" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F50" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G50" s="9"/>
-      <c r="H50" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I50" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J50" s="14"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
+      <c r="H50" s="46"/>
+      <c r="I50" s="47"/>
+      <c r="J50" s="48"/>
+      <c r="K50" s="37"/>
+      <c r="L50" s="37"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
       <c r="O50" s="6"/>
@@ -4770,28 +4627,24 @@
       <c r="BP50" s="2"/>
     </row>
     <row r="51" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="29"/>
+      <c r="A51" s="3"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="8"/>
-      <c r="E51" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F51" s="23">
-        <f t="shared" si="3"/>
+      <c r="E51" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F51" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G51" s="9"/>
-      <c r="H51" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I51" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J51" s="14"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="6"/>
+      <c r="H51" s="46"/>
+      <c r="I51" s="47"/>
+      <c r="J51" s="48"/>
+      <c r="K51" s="37"/>
+      <c r="L51" s="37"/>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
       <c r="O51" s="6"/>
@@ -4850,28 +4703,24 @@
       <c r="BP51" s="2"/>
     </row>
     <row r="52" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="3"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
+      <c r="A52" s="22"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
       <c r="D52" s="8"/>
-      <c r="E52" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F52" s="23">
-        <f t="shared" si="3"/>
+      <c r="E52" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F52" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G52" s="9"/>
-      <c r="H52" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I52" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J52" s="14"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
+      <c r="H52" s="46"/>
+      <c r="I52" s="47"/>
+      <c r="J52" s="48"/>
+      <c r="K52" s="37"/>
+      <c r="L52" s="37"/>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
       <c r="O52" s="6"/>
@@ -4930,28 +4779,24 @@
       <c r="BP52" s="2"/>
     </row>
     <row r="53" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="3"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
+      <c r="A53" s="22"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
       <c r="D53" s="8"/>
-      <c r="E53" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F53" s="23">
-        <f t="shared" si="3"/>
+      <c r="E53" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F53" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G53" s="9"/>
-      <c r="H53" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I53" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J53" s="14"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
+      <c r="H53" s="46"/>
+      <c r="I53" s="47"/>
+      <c r="J53" s="48"/>
+      <c r="K53" s="37"/>
+      <c r="L53" s="37"/>
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
       <c r="O53" s="6"/>
@@ -5010,28 +4855,24 @@
       <c r="BP53" s="2"/>
     </row>
     <row r="54" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="26"/>
-      <c r="B54" s="27"/>
-      <c r="C54" s="27"/>
+      <c r="A54" s="11"/>
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
       <c r="D54" s="8"/>
-      <c r="E54" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F54" s="23">
-        <f t="shared" si="3"/>
+      <c r="E54" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F54" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G54" s="9"/>
-      <c r="H54" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I54" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J54" s="14"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
+      <c r="H54" s="46"/>
+      <c r="I54" s="47"/>
+      <c r="J54" s="48"/>
+      <c r="K54" s="37"/>
+      <c r="L54" s="37"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
       <c r="O54" s="6"/>
@@ -5090,28 +4931,24 @@
       <c r="BP54" s="2"/>
     </row>
     <row r="55" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="29"/>
+      <c r="A55" s="19"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="8"/>
-      <c r="E55" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F55" s="23">
-        <f t="shared" si="3"/>
+      <c r="E55" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F55" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G55" s="9"/>
-      <c r="H55" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I55" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J55" s="14"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="6"/>
+      <c r="H55" s="46"/>
+      <c r="I55" s="47"/>
+      <c r="J55" s="48"/>
+      <c r="K55" s="37"/>
+      <c r="L55" s="37"/>
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
       <c r="O55" s="6"/>
@@ -5170,28 +5007,24 @@
       <c r="BP55" s="2"/>
     </row>
     <row r="56" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="3"/>
-      <c r="B56" s="30"/>
-      <c r="C56" s="30"/>
+      <c r="A56" s="17"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
       <c r="D56" s="8"/>
-      <c r="E56" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F56" s="23">
-        <f t="shared" si="3"/>
+      <c r="E56" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F56" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G56" s="9"/>
-      <c r="H56" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I56" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J56" s="14"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="6"/>
+      <c r="H56" s="46"/>
+      <c r="I56" s="47"/>
+      <c r="J56" s="48"/>
+      <c r="K56" s="37"/>
+      <c r="L56" s="37"/>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
       <c r="O56" s="6"/>
@@ -5250,28 +5083,24 @@
       <c r="BP56" s="2"/>
     </row>
     <row r="57" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="3"/>
-      <c r="B57" s="30"/>
-      <c r="C57" s="30"/>
+      <c r="A57" s="19"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
       <c r="D57" s="8"/>
-      <c r="E57" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F57" s="23">
-        <f t="shared" si="3"/>
+      <c r="E57" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F57" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G57" s="9"/>
-      <c r="H57" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I57" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J57" s="14"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="6"/>
+      <c r="H57" s="46"/>
+      <c r="I57" s="47"/>
+      <c r="J57" s="48"/>
+      <c r="K57" s="37"/>
+      <c r="L57" s="37"/>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
       <c r="O57" s="6"/>
@@ -5330,28 +5159,24 @@
       <c r="BP57" s="2"/>
     </row>
     <row r="58" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="3"/>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
+      <c r="A58" s="19"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
       <c r="D58" s="8"/>
-      <c r="E58" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F58" s="23">
-        <f t="shared" si="3"/>
+      <c r="E58" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F58" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G58" s="9"/>
-      <c r="H58" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I58" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J58" s="14"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
+      <c r="H58" s="46"/>
+      <c r="I58" s="47"/>
+      <c r="J58" s="48"/>
+      <c r="K58" s="37"/>
+      <c r="L58" s="37"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
       <c r="O58" s="6"/>
@@ -5410,28 +5235,24 @@
       <c r="BP58" s="2"/>
     </row>
     <row r="59" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="29"/>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
+      <c r="A59" s="24"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="20"/>
       <c r="D59" s="8"/>
-      <c r="E59" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F59" s="23">
-        <f t="shared" si="3"/>
+      <c r="E59" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F59" s="16">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G59" s="9"/>
-      <c r="H59" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I59" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J59" s="14"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
+      <c r="H59" s="46"/>
+      <c r="I59" s="47"/>
+      <c r="J59" s="48"/>
+      <c r="K59" s="37"/>
+      <c r="L59" s="37"/>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
       <c r="O59" s="6"/>
@@ -5489,18 +5310,25 @@
       <c r="BO59" s="2"/>
       <c r="BP59" s="2"/>
     </row>
-    <row r="60" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="2"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="20"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
+    <row r="60" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="19"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F60" s="16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G60" s="9"/>
+      <c r="H60" s="46"/>
+      <c r="I60" s="47"/>
+      <c r="J60" s="48"/>
+      <c r="K60" s="37"/>
+      <c r="L60" s="37"/>
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
       <c r="O60" s="6"/>
@@ -5558,18 +5386,25 @@
       <c r="BO60" s="2"/>
       <c r="BP60" s="2"/>
     </row>
-    <row r="61" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="2"/>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="20"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="6"/>
+    <row r="61" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="3"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F61" s="16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G61" s="9"/>
+      <c r="H61" s="46"/>
+      <c r="I61" s="47"/>
+      <c r="J61" s="48"/>
+      <c r="K61" s="37"/>
+      <c r="L61" s="37"/>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
       <c r="O61" s="6"/>
@@ -5627,18 +5462,25 @@
       <c r="BO61" s="2"/>
       <c r="BP61" s="2"/>
     </row>
-    <row r="62" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="2"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="19"/>
-      <c r="F62" s="20"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="6"/>
+    <row r="62" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="3"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F62" s="16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G62" s="9"/>
+      <c r="H62" s="46"/>
+      <c r="I62" s="47"/>
+      <c r="J62" s="48"/>
+      <c r="K62" s="37"/>
+      <c r="L62" s="37"/>
       <c r="M62" s="6"/>
       <c r="N62" s="6"/>
       <c r="O62" s="6"/>
@@ -5696,18 +5538,25 @@
       <c r="BO62" s="2"/>
       <c r="BP62" s="2"/>
     </row>
-    <row r="63" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="2"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="19"/>
-      <c r="F63" s="20"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
+    <row r="63" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="19"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F63" s="16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G63" s="9"/>
+      <c r="H63" s="46"/>
+      <c r="I63" s="47"/>
+      <c r="J63" s="48"/>
+      <c r="K63" s="37"/>
+      <c r="L63" s="37"/>
       <c r="M63" s="6"/>
       <c r="N63" s="6"/>
       <c r="O63" s="6"/>
@@ -5765,18 +5614,25 @@
       <c r="BO63" s="2"/>
       <c r="BP63" s="2"/>
     </row>
-    <row r="64" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="2"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="20"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6"/>
-      <c r="L64" s="6"/>
+    <row r="64" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="19"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F64" s="16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G64" s="9"/>
+      <c r="H64" s="46"/>
+      <c r="I64" s="47"/>
+      <c r="J64" s="48"/>
+      <c r="K64" s="37"/>
+      <c r="L64" s="37"/>
       <c r="M64" s="6"/>
       <c r="N64" s="6"/>
       <c r="O64" s="6"/>
@@ -5834,18 +5690,25 @@
       <c r="BO64" s="2"/>
       <c r="BP64" s="2"/>
     </row>
-    <row r="65" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="2"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="20"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
-      <c r="L65" s="6"/>
+    <row r="65" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="19"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F65" s="16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G65" s="9"/>
+      <c r="H65" s="46"/>
+      <c r="I65" s="47"/>
+      <c r="J65" s="48"/>
+      <c r="K65" s="37"/>
+      <c r="L65" s="37"/>
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
       <c r="O65" s="6"/>
@@ -5903,18 +5766,25 @@
       <c r="BO65" s="2"/>
       <c r="BP65" s="2"/>
     </row>
-    <row r="66" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="2"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="19"/>
-      <c r="E66" s="19"/>
-      <c r="F66" s="20"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
+    <row r="66" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="17"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="15">
+        <f t="shared" ref="E66:E74" si="6">+D66*0.21</f>
+        <v>0</v>
+      </c>
+      <c r="F66" s="16">
+        <f t="shared" ref="F66:F74" si="7">+E66+D66</f>
+        <v>0</v>
+      </c>
+      <c r="G66" s="9"/>
+      <c r="H66" s="46"/>
+      <c r="I66" s="47"/>
+      <c r="J66" s="48"/>
+      <c r="K66" s="37"/>
+      <c r="L66" s="37"/>
       <c r="M66" s="6"/>
       <c r="N66" s="6"/>
       <c r="O66" s="6"/>
@@ -5972,18 +5842,25 @@
       <c r="BO66" s="2"/>
       <c r="BP66" s="2"/>
     </row>
-    <row r="67" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="2"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="19"/>
-      <c r="E67" s="19"/>
-      <c r="F67" s="20"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="6"/>
-      <c r="L67" s="6"/>
+    <row r="67" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="19"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="15">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F67" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G67" s="9"/>
+      <c r="H67" s="46"/>
+      <c r="I67" s="47"/>
+      <c r="J67" s="48"/>
+      <c r="K67" s="37"/>
+      <c r="L67" s="37"/>
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
       <c r="O67" s="6"/>
@@ -6041,18 +5918,25 @@
       <c r="BO67" s="2"/>
       <c r="BP67" s="2"/>
     </row>
-    <row r="68" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="2"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="19"/>
-      <c r="E68" s="19"/>
-      <c r="F68" s="20"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="6"/>
-      <c r="L68" s="6"/>
+    <row r="68" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="19"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="15">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F68" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G68" s="9"/>
+      <c r="H68" s="46"/>
+      <c r="I68" s="47"/>
+      <c r="J68" s="48"/>
+      <c r="K68" s="37"/>
+      <c r="L68" s="37"/>
       <c r="M68" s="6"/>
       <c r="N68" s="6"/>
       <c r="O68" s="6"/>
@@ -6110,18 +5994,25 @@
       <c r="BO68" s="2"/>
       <c r="BP68" s="2"/>
     </row>
-    <row r="69" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="2"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="19"/>
-      <c r="F69" s="20"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="6"/>
-      <c r="L69" s="6"/>
+    <row r="69" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="3"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="28"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="15">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F69" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G69" s="9"/>
+      <c r="H69" s="46"/>
+      <c r="I69" s="47"/>
+      <c r="J69" s="48"/>
+      <c r="K69" s="37"/>
+      <c r="L69" s="37"/>
       <c r="M69" s="6"/>
       <c r="N69" s="6"/>
       <c r="O69" s="6"/>
@@ -6179,18 +6070,25 @@
       <c r="BO69" s="2"/>
       <c r="BP69" s="2"/>
     </row>
-    <row r="70" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="2"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="19"/>
-      <c r="E70" s="19"/>
-      <c r="F70" s="20"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="6"/>
-      <c r="L70" s="6"/>
+    <row r="70" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="3"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="15">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F70" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G70" s="9"/>
+      <c r="H70" s="46"/>
+      <c r="I70" s="47"/>
+      <c r="J70" s="48"/>
+      <c r="K70" s="37"/>
+      <c r="L70" s="37"/>
       <c r="M70" s="6"/>
       <c r="N70" s="6"/>
       <c r="O70" s="6"/>
@@ -6248,18 +6146,25 @@
       <c r="BO70" s="2"/>
       <c r="BP70" s="2"/>
     </row>
-    <row r="71" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="2"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="19"/>
-      <c r="E71" s="19"/>
-      <c r="F71" s="20"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
-      <c r="J71" s="6"/>
-      <c r="K71" s="6"/>
-      <c r="L71" s="6"/>
+    <row r="71" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="17"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="15">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F71" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G71" s="9"/>
+      <c r="H71" s="46"/>
+      <c r="I71" s="47"/>
+      <c r="J71" s="48"/>
+      <c r="K71" s="37"/>
+      <c r="L71" s="37"/>
       <c r="M71" s="6"/>
       <c r="N71" s="6"/>
       <c r="O71" s="6"/>
@@ -6317,18 +6222,25 @@
       <c r="BO71" s="2"/>
       <c r="BP71" s="2"/>
     </row>
-    <row r="72" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="2"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="19"/>
-      <c r="E72" s="19"/>
-      <c r="F72" s="20"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="6"/>
-      <c r="L72" s="6"/>
+    <row r="72" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="25"/>
+      <c r="B72" s="31"/>
+      <c r="C72" s="33"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="15">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F72" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G72" s="9"/>
+      <c r="H72" s="46"/>
+      <c r="I72" s="47"/>
+      <c r="J72" s="48"/>
+      <c r="K72" s="37"/>
+      <c r="L72" s="37"/>
       <c r="M72" s="6"/>
       <c r="N72" s="6"/>
       <c r="O72" s="6"/>
@@ -6386,18 +6298,25 @@
       <c r="BO72" s="2"/>
       <c r="BP72" s="2"/>
     </row>
-    <row r="73" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="2"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="20"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="6"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="6"/>
-      <c r="L73" s="6"/>
+    <row r="73" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="19"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="15">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F73" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G73" s="9"/>
+      <c r="H73" s="46"/>
+      <c r="I73" s="47"/>
+      <c r="J73" s="48"/>
+      <c r="K73" s="37"/>
+      <c r="L73" s="37"/>
       <c r="M73" s="6"/>
       <c r="N73" s="6"/>
       <c r="O73" s="6"/>
@@ -6455,18 +6374,25 @@
       <c r="BO73" s="2"/>
       <c r="BP73" s="2"/>
     </row>
-    <row r="74" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="2"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="19"/>
-      <c r="E74" s="19"/>
-      <c r="F74" s="20"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
+    <row r="74" spans="1:68" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="19"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="15">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F74" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G74" s="9"/>
+      <c r="H74" s="46"/>
+      <c r="I74" s="47"/>
+      <c r="J74" s="48"/>
+      <c r="K74" s="37"/>
+      <c r="L74" s="37"/>
       <c r="M74" s="6"/>
       <c r="N74" s="6"/>
       <c r="O74" s="6"/>
@@ -6524,2355 +6450,9 @@
       <c r="BO74" s="2"/>
       <c r="BP74" s="2"/>
     </row>
-    <row r="75" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="2"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="19"/>
-      <c r="E75" s="19"/>
-      <c r="F75" s="20"/>
-      <c r="H75" s="6"/>
-      <c r="I75" s="6"/>
-      <c r="J75" s="6"/>
-      <c r="K75" s="6"/>
-      <c r="L75" s="6"/>
-      <c r="M75" s="6"/>
-      <c r="N75" s="6"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="6"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="6"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="6"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="6"/>
-      <c r="AB75" s="6"/>
-      <c r="AC75" s="6"/>
-      <c r="AD75" s="6"/>
-      <c r="AE75" s="6"/>
-      <c r="AF75" s="6"/>
-      <c r="AG75" s="6"/>
-      <c r="AH75" s="6"/>
-      <c r="AI75" s="6"/>
-      <c r="AJ75" s="6"/>
-      <c r="AK75" s="6"/>
-      <c r="AL75" s="6"/>
-      <c r="AM75" s="2"/>
-      <c r="AN75" s="2"/>
-      <c r="AO75" s="2"/>
-      <c r="AP75" s="2"/>
-      <c r="AQ75" s="2"/>
-      <c r="AR75" s="2"/>
-      <c r="AS75" s="2"/>
-      <c r="AT75" s="2"/>
-      <c r="AU75" s="2"/>
-      <c r="AV75" s="2"/>
-      <c r="AW75" s="2"/>
-      <c r="AX75" s="2"/>
-      <c r="AY75" s="2"/>
-      <c r="AZ75" s="2"/>
-      <c r="BA75" s="2"/>
-      <c r="BB75" s="2"/>
-      <c r="BC75" s="2"/>
-      <c r="BD75" s="2"/>
-      <c r="BE75" s="2"/>
-      <c r="BF75" s="2"/>
-      <c r="BG75" s="2"/>
-      <c r="BH75" s="2"/>
-      <c r="BI75" s="2"/>
-      <c r="BJ75" s="2"/>
-      <c r="BK75" s="2"/>
-      <c r="BL75" s="2"/>
-      <c r="BM75" s="2"/>
-      <c r="BN75" s="2"/>
-      <c r="BO75" s="2"/>
-      <c r="BP75" s="2"/>
-    </row>
-    <row r="76" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="2"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="20"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
-      <c r="J76" s="6"/>
-      <c r="K76" s="6"/>
-      <c r="L76" s="6"/>
-      <c r="M76" s="6"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="6"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="6"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="6"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="6"/>
-      <c r="AB76" s="6"/>
-      <c r="AC76" s="6"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="2"/>
-      <c r="AN76" s="2"/>
-      <c r="AO76" s="2"/>
-      <c r="AP76" s="2"/>
-      <c r="AQ76" s="2"/>
-      <c r="AR76" s="2"/>
-      <c r="AS76" s="2"/>
-      <c r="AT76" s="2"/>
-      <c r="AU76" s="2"/>
-      <c r="AV76" s="2"/>
-      <c r="AW76" s="2"/>
-      <c r="AX76" s="2"/>
-      <c r="AY76" s="2"/>
-      <c r="AZ76" s="2"/>
-      <c r="BA76" s="2"/>
-      <c r="BB76" s="2"/>
-      <c r="BC76" s="2"/>
-      <c r="BD76" s="2"/>
-      <c r="BE76" s="2"/>
-      <c r="BF76" s="2"/>
-      <c r="BG76" s="2"/>
-      <c r="BH76" s="2"/>
-      <c r="BI76" s="2"/>
-      <c r="BJ76" s="2"/>
-      <c r="BK76" s="2"/>
-      <c r="BL76" s="2"/>
-      <c r="BM76" s="2"/>
-      <c r="BN76" s="2"/>
-      <c r="BO76" s="2"/>
-      <c r="BP76" s="2"/>
-    </row>
-    <row r="77" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="2"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="19"/>
-      <c r="E77" s="19"/>
-      <c r="F77" s="20"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="6"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="6"/>
-      <c r="L77" s="6"/>
-      <c r="M77" s="6"/>
-      <c r="N77" s="6"/>
-      <c r="O77" s="6"/>
-      <c r="P77" s="6"/>
-      <c r="Q77" s="6"/>
-      <c r="R77" s="6"/>
-      <c r="S77" s="6"/>
-      <c r="T77" s="6"/>
-      <c r="U77" s="6"/>
-      <c r="V77" s="6"/>
-      <c r="W77" s="6"/>
-      <c r="X77" s="6"/>
-      <c r="Y77" s="6"/>
-      <c r="Z77" s="6"/>
-      <c r="AA77" s="6"/>
-      <c r="AB77" s="6"/>
-      <c r="AC77" s="6"/>
-      <c r="AD77" s="6"/>
-      <c r="AE77" s="6"/>
-      <c r="AF77" s="6"/>
-      <c r="AG77" s="6"/>
-      <c r="AH77" s="6"/>
-      <c r="AI77" s="6"/>
-      <c r="AJ77" s="6"/>
-      <c r="AK77" s="6"/>
-      <c r="AL77" s="6"/>
-      <c r="AM77" s="2"/>
-      <c r="AN77" s="2"/>
-      <c r="AO77" s="2"/>
-      <c r="AP77" s="2"/>
-      <c r="AQ77" s="2"/>
-      <c r="AR77" s="2"/>
-      <c r="AS77" s="2"/>
-      <c r="AT77" s="2"/>
-      <c r="AU77" s="2"/>
-      <c r="AV77" s="2"/>
-      <c r="AW77" s="2"/>
-      <c r="AX77" s="2"/>
-      <c r="AY77" s="2"/>
-      <c r="AZ77" s="2"/>
-      <c r="BA77" s="2"/>
-      <c r="BB77" s="2"/>
-      <c r="BC77" s="2"/>
-      <c r="BD77" s="2"/>
-      <c r="BE77" s="2"/>
-      <c r="BF77" s="2"/>
-      <c r="BG77" s="2"/>
-      <c r="BH77" s="2"/>
-      <c r="BI77" s="2"/>
-      <c r="BJ77" s="2"/>
-      <c r="BK77" s="2"/>
-      <c r="BL77" s="2"/>
-      <c r="BM77" s="2"/>
-      <c r="BN77" s="2"/>
-      <c r="BO77" s="2"/>
-      <c r="BP77" s="2"/>
-    </row>
-    <row r="78" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="2"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="19"/>
-      <c r="E78" s="19"/>
-      <c r="F78" s="20"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6"/>
-      <c r="L78" s="6"/>
-      <c r="M78" s="6"/>
-      <c r="N78" s="6"/>
-      <c r="O78" s="6"/>
-      <c r="P78" s="6"/>
-      <c r="Q78" s="6"/>
-      <c r="R78" s="6"/>
-      <c r="S78" s="6"/>
-      <c r="T78" s="6"/>
-      <c r="U78" s="6"/>
-      <c r="V78" s="6"/>
-      <c r="W78" s="6"/>
-      <c r="X78" s="6"/>
-      <c r="Y78" s="6"/>
-      <c r="Z78" s="6"/>
-      <c r="AA78" s="6"/>
-      <c r="AB78" s="6"/>
-      <c r="AC78" s="6"/>
-      <c r="AD78" s="6"/>
-      <c r="AE78" s="6"/>
-      <c r="AF78" s="6"/>
-      <c r="AG78" s="6"/>
-      <c r="AH78" s="6"/>
-      <c r="AI78" s="6"/>
-      <c r="AJ78" s="6"/>
-      <c r="AK78" s="6"/>
-      <c r="AL78" s="6"/>
-      <c r="AM78" s="2"/>
-      <c r="AN78" s="2"/>
-      <c r="AO78" s="2"/>
-      <c r="AP78" s="2"/>
-      <c r="AQ78" s="2"/>
-      <c r="AR78" s="2"/>
-      <c r="AS78" s="2"/>
-      <c r="AT78" s="2"/>
-      <c r="AU78" s="2"/>
-      <c r="AV78" s="2"/>
-      <c r="AW78" s="2"/>
-      <c r="AX78" s="2"/>
-      <c r="AY78" s="2"/>
-      <c r="AZ78" s="2"/>
-      <c r="BA78" s="2"/>
-      <c r="BB78" s="2"/>
-      <c r="BC78" s="2"/>
-      <c r="BD78" s="2"/>
-      <c r="BE78" s="2"/>
-      <c r="BF78" s="2"/>
-      <c r="BG78" s="2"/>
-      <c r="BH78" s="2"/>
-      <c r="BI78" s="2"/>
-      <c r="BJ78" s="2"/>
-      <c r="BK78" s="2"/>
-      <c r="BL78" s="2"/>
-      <c r="BM78" s="2"/>
-      <c r="BN78" s="2"/>
-      <c r="BO78" s="2"/>
-      <c r="BP78" s="2"/>
-    </row>
-    <row r="79" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="2"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="19"/>
-      <c r="E79" s="19"/>
-      <c r="F79" s="20"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
-      <c r="J79" s="6"/>
-      <c r="K79" s="6"/>
-      <c r="L79" s="6"/>
-      <c r="M79" s="6"/>
-      <c r="N79" s="6"/>
-      <c r="O79" s="6"/>
-      <c r="P79" s="6"/>
-      <c r="Q79" s="6"/>
-      <c r="R79" s="6"/>
-      <c r="S79" s="6"/>
-      <c r="T79" s="6"/>
-      <c r="U79" s="6"/>
-      <c r="V79" s="6"/>
-      <c r="W79" s="6"/>
-      <c r="X79" s="6"/>
-      <c r="Y79" s="6"/>
-      <c r="Z79" s="6"/>
-      <c r="AA79" s="6"/>
-      <c r="AB79" s="6"/>
-      <c r="AC79" s="6"/>
-      <c r="AD79" s="6"/>
-      <c r="AE79" s="6"/>
-      <c r="AF79" s="6"/>
-      <c r="AG79" s="6"/>
-      <c r="AH79" s="6"/>
-      <c r="AI79" s="6"/>
-      <c r="AJ79" s="6"/>
-      <c r="AK79" s="6"/>
-      <c r="AL79" s="6"/>
-      <c r="AM79" s="2"/>
-      <c r="AN79" s="2"/>
-      <c r="AO79" s="2"/>
-      <c r="AP79" s="2"/>
-      <c r="AQ79" s="2"/>
-      <c r="AR79" s="2"/>
-      <c r="AS79" s="2"/>
-      <c r="AT79" s="2"/>
-      <c r="AU79" s="2"/>
-      <c r="AV79" s="2"/>
-      <c r="AW79" s="2"/>
-      <c r="AX79" s="2"/>
-      <c r="AY79" s="2"/>
-      <c r="AZ79" s="2"/>
-      <c r="BA79" s="2"/>
-      <c r="BB79" s="2"/>
-      <c r="BC79" s="2"/>
-      <c r="BD79" s="2"/>
-      <c r="BE79" s="2"/>
-      <c r="BF79" s="2"/>
-      <c r="BG79" s="2"/>
-      <c r="BH79" s="2"/>
-      <c r="BI79" s="2"/>
-      <c r="BJ79" s="2"/>
-      <c r="BK79" s="2"/>
-      <c r="BL79" s="2"/>
-      <c r="BM79" s="2"/>
-      <c r="BN79" s="2"/>
-      <c r="BO79" s="2"/>
-      <c r="BP79" s="2"/>
-    </row>
-    <row r="80" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="2"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="19"/>
-      <c r="E80" s="19"/>
-      <c r="F80" s="20"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="J80" s="6"/>
-      <c r="K80" s="6"/>
-      <c r="L80" s="6"/>
-      <c r="M80" s="6"/>
-      <c r="N80" s="6"/>
-      <c r="O80" s="6"/>
-      <c r="P80" s="6"/>
-      <c r="Q80" s="6"/>
-      <c r="R80" s="6"/>
-      <c r="S80" s="6"/>
-      <c r="T80" s="6"/>
-      <c r="U80" s="6"/>
-      <c r="V80" s="6"/>
-      <c r="W80" s="6"/>
-      <c r="X80" s="6"/>
-      <c r="Y80" s="6"/>
-      <c r="Z80" s="6"/>
-      <c r="AA80" s="6"/>
-      <c r="AB80" s="6"/>
-      <c r="AC80" s="6"/>
-      <c r="AD80" s="6"/>
-      <c r="AE80" s="6"/>
-      <c r="AF80" s="6"/>
-      <c r="AG80" s="6"/>
-      <c r="AH80" s="6"/>
-      <c r="AI80" s="6"/>
-      <c r="AJ80" s="6"/>
-      <c r="AK80" s="6"/>
-      <c r="AL80" s="6"/>
-      <c r="AM80" s="2"/>
-      <c r="AN80" s="2"/>
-      <c r="AO80" s="2"/>
-      <c r="AP80" s="2"/>
-      <c r="AQ80" s="2"/>
-      <c r="AR80" s="2"/>
-      <c r="AS80" s="2"/>
-      <c r="AT80" s="2"/>
-      <c r="AU80" s="2"/>
-      <c r="AV80" s="2"/>
-      <c r="AW80" s="2"/>
-      <c r="AX80" s="2"/>
-      <c r="AY80" s="2"/>
-      <c r="AZ80" s="2"/>
-      <c r="BA80" s="2"/>
-      <c r="BB80" s="2"/>
-      <c r="BC80" s="2"/>
-      <c r="BD80" s="2"/>
-      <c r="BE80" s="2"/>
-      <c r="BF80" s="2"/>
-      <c r="BG80" s="2"/>
-      <c r="BH80" s="2"/>
-      <c r="BI80" s="2"/>
-      <c r="BJ80" s="2"/>
-      <c r="BK80" s="2"/>
-      <c r="BL80" s="2"/>
-      <c r="BM80" s="2"/>
-      <c r="BN80" s="2"/>
-      <c r="BO80" s="2"/>
-      <c r="BP80" s="2"/>
-    </row>
-    <row r="81" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="2"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="19"/>
-      <c r="E81" s="19"/>
-      <c r="F81" s="20"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
-      <c r="J81" s="6"/>
-      <c r="K81" s="6"/>
-      <c r="L81" s="6"/>
-      <c r="M81" s="6"/>
-      <c r="N81" s="6"/>
-      <c r="O81" s="6"/>
-      <c r="P81" s="6"/>
-      <c r="Q81" s="6"/>
-      <c r="R81" s="6"/>
-      <c r="S81" s="6"/>
-      <c r="T81" s="6"/>
-      <c r="U81" s="6"/>
-      <c r="V81" s="6"/>
-      <c r="W81" s="6"/>
-      <c r="X81" s="6"/>
-      <c r="Y81" s="6"/>
-      <c r="Z81" s="6"/>
-      <c r="AA81" s="6"/>
-      <c r="AB81" s="6"/>
-      <c r="AC81" s="6"/>
-      <c r="AD81" s="6"/>
-      <c r="AE81" s="6"/>
-      <c r="AF81" s="6"/>
-      <c r="AG81" s="6"/>
-      <c r="AH81" s="6"/>
-      <c r="AI81" s="6"/>
-      <c r="AJ81" s="6"/>
-      <c r="AK81" s="6"/>
-      <c r="AL81" s="6"/>
-      <c r="AM81" s="2"/>
-      <c r="AN81" s="2"/>
-      <c r="AO81" s="2"/>
-      <c r="AP81" s="2"/>
-      <c r="AQ81" s="2"/>
-      <c r="AR81" s="2"/>
-      <c r="AS81" s="2"/>
-      <c r="AT81" s="2"/>
-      <c r="AU81" s="2"/>
-      <c r="AV81" s="2"/>
-      <c r="AW81" s="2"/>
-      <c r="AX81" s="2"/>
-      <c r="AY81" s="2"/>
-      <c r="AZ81" s="2"/>
-      <c r="BA81" s="2"/>
-      <c r="BB81" s="2"/>
-      <c r="BC81" s="2"/>
-      <c r="BD81" s="2"/>
-      <c r="BE81" s="2"/>
-      <c r="BF81" s="2"/>
-      <c r="BG81" s="2"/>
-      <c r="BH81" s="2"/>
-      <c r="BI81" s="2"/>
-      <c r="BJ81" s="2"/>
-      <c r="BK81" s="2"/>
-      <c r="BL81" s="2"/>
-      <c r="BM81" s="2"/>
-      <c r="BN81" s="2"/>
-      <c r="BO81" s="2"/>
-      <c r="BP81" s="2"/>
-    </row>
-    <row r="82" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="2"/>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="19"/>
-      <c r="E82" s="19"/>
-      <c r="F82" s="20"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="6"/>
-      <c r="J82" s="6"/>
-      <c r="K82" s="6"/>
-      <c r="L82" s="6"/>
-      <c r="M82" s="6"/>
-      <c r="N82" s="6"/>
-      <c r="O82" s="6"/>
-      <c r="P82" s="6"/>
-      <c r="Q82" s="6"/>
-      <c r="R82" s="6"/>
-      <c r="S82" s="6"/>
-      <c r="T82" s="6"/>
-      <c r="U82" s="6"/>
-      <c r="V82" s="6"/>
-      <c r="W82" s="6"/>
-      <c r="X82" s="6"/>
-      <c r="Y82" s="6"/>
-      <c r="Z82" s="6"/>
-      <c r="AA82" s="6"/>
-      <c r="AB82" s="6"/>
-      <c r="AC82" s="6"/>
-      <c r="AD82" s="6"/>
-      <c r="AE82" s="6"/>
-      <c r="AF82" s="6"/>
-      <c r="AG82" s="6"/>
-      <c r="AH82" s="6"/>
-      <c r="AI82" s="6"/>
-      <c r="AJ82" s="6"/>
-      <c r="AK82" s="6"/>
-      <c r="AL82" s="6"/>
-      <c r="AM82" s="2"/>
-      <c r="AN82" s="2"/>
-      <c r="AO82" s="2"/>
-      <c r="AP82" s="2"/>
-      <c r="AQ82" s="2"/>
-      <c r="AR82" s="2"/>
-      <c r="AS82" s="2"/>
-      <c r="AT82" s="2"/>
-      <c r="AU82" s="2"/>
-      <c r="AV82" s="2"/>
-      <c r="AW82" s="2"/>
-      <c r="AX82" s="2"/>
-      <c r="AY82" s="2"/>
-      <c r="AZ82" s="2"/>
-      <c r="BA82" s="2"/>
-      <c r="BB82" s="2"/>
-      <c r="BC82" s="2"/>
-      <c r="BD82" s="2"/>
-      <c r="BE82" s="2"/>
-      <c r="BF82" s="2"/>
-      <c r="BG82" s="2"/>
-      <c r="BH82" s="2"/>
-      <c r="BI82" s="2"/>
-      <c r="BJ82" s="2"/>
-      <c r="BK82" s="2"/>
-      <c r="BL82" s="2"/>
-      <c r="BM82" s="2"/>
-      <c r="BN82" s="2"/>
-      <c r="BO82" s="2"/>
-      <c r="BP82" s="2"/>
-    </row>
-    <row r="83" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="2"/>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="19"/>
-      <c r="E83" s="19"/>
-      <c r="F83" s="20"/>
-      <c r="H83" s="6"/>
-      <c r="I83" s="6"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6"/>
-      <c r="L83" s="6"/>
-      <c r="M83" s="6"/>
-      <c r="N83" s="6"/>
-      <c r="O83" s="6"/>
-      <c r="P83" s="6"/>
-      <c r="Q83" s="6"/>
-      <c r="R83" s="6"/>
-      <c r="S83" s="6"/>
-      <c r="T83" s="6"/>
-      <c r="U83" s="6"/>
-      <c r="V83" s="6"/>
-      <c r="W83" s="6"/>
-      <c r="X83" s="6"/>
-      <c r="Y83" s="6"/>
-      <c r="Z83" s="6"/>
-      <c r="AA83" s="6"/>
-      <c r="AB83" s="6"/>
-      <c r="AC83" s="6"/>
-      <c r="AD83" s="6"/>
-      <c r="AE83" s="6"/>
-      <c r="AF83" s="6"/>
-      <c r="AG83" s="6"/>
-      <c r="AH83" s="6"/>
-      <c r="AI83" s="6"/>
-      <c r="AJ83" s="6"/>
-      <c r="AK83" s="6"/>
-      <c r="AL83" s="6"/>
-      <c r="AM83" s="2"/>
-      <c r="AN83" s="2"/>
-      <c r="AO83" s="2"/>
-      <c r="AP83" s="2"/>
-      <c r="AQ83" s="2"/>
-      <c r="AR83" s="2"/>
-      <c r="AS83" s="2"/>
-      <c r="AT83" s="2"/>
-      <c r="AU83" s="2"/>
-      <c r="AV83" s="2"/>
-      <c r="AW83" s="2"/>
-      <c r="AX83" s="2"/>
-      <c r="AY83" s="2"/>
-      <c r="AZ83" s="2"/>
-      <c r="BA83" s="2"/>
-      <c r="BB83" s="2"/>
-      <c r="BC83" s="2"/>
-      <c r="BD83" s="2"/>
-      <c r="BE83" s="2"/>
-      <c r="BF83" s="2"/>
-      <c r="BG83" s="2"/>
-      <c r="BH83" s="2"/>
-      <c r="BI83" s="2"/>
-      <c r="BJ83" s="2"/>
-      <c r="BK83" s="2"/>
-      <c r="BL83" s="2"/>
-      <c r="BM83" s="2"/>
-      <c r="BN83" s="2"/>
-      <c r="BO83" s="2"/>
-      <c r="BP83" s="2"/>
-    </row>
-    <row r="84" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="2"/>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="19"/>
-      <c r="E84" s="19"/>
-      <c r="F84" s="20"/>
-      <c r="H84" s="6"/>
-      <c r="I84" s="6"/>
-      <c r="J84" s="6"/>
-      <c r="K84" s="6"/>
-      <c r="L84" s="6"/>
-      <c r="M84" s="6"/>
-      <c r="N84" s="6"/>
-      <c r="O84" s="6"/>
-      <c r="P84" s="6"/>
-      <c r="Q84" s="6"/>
-      <c r="R84" s="6"/>
-      <c r="S84" s="6"/>
-      <c r="T84" s="6"/>
-      <c r="U84" s="6"/>
-      <c r="V84" s="6"/>
-      <c r="W84" s="6"/>
-      <c r="X84" s="6"/>
-      <c r="Y84" s="6"/>
-      <c r="Z84" s="6"/>
-      <c r="AA84" s="6"/>
-      <c r="AB84" s="6"/>
-      <c r="AC84" s="6"/>
-      <c r="AD84" s="6"/>
-      <c r="AE84" s="6"/>
-      <c r="AF84" s="6"/>
-      <c r="AG84" s="6"/>
-      <c r="AH84" s="6"/>
-      <c r="AI84" s="6"/>
-      <c r="AJ84" s="6"/>
-      <c r="AK84" s="6"/>
-      <c r="AL84" s="6"/>
-      <c r="AM84" s="2"/>
-      <c r="AN84" s="2"/>
-      <c r="AO84" s="2"/>
-      <c r="AP84" s="2"/>
-      <c r="AQ84" s="2"/>
-      <c r="AR84" s="2"/>
-      <c r="AS84" s="2"/>
-      <c r="AT84" s="2"/>
-      <c r="AU84" s="2"/>
-      <c r="AV84" s="2"/>
-      <c r="AW84" s="2"/>
-      <c r="AX84" s="2"/>
-      <c r="AY84" s="2"/>
-      <c r="AZ84" s="2"/>
-      <c r="BA84" s="2"/>
-      <c r="BB84" s="2"/>
-      <c r="BC84" s="2"/>
-      <c r="BD84" s="2"/>
-      <c r="BE84" s="2"/>
-      <c r="BF84" s="2"/>
-      <c r="BG84" s="2"/>
-      <c r="BH84" s="2"/>
-      <c r="BI84" s="2"/>
-      <c r="BJ84" s="2"/>
-      <c r="BK84" s="2"/>
-      <c r="BL84" s="2"/>
-      <c r="BM84" s="2"/>
-      <c r="BN84" s="2"/>
-      <c r="BO84" s="2"/>
-      <c r="BP84" s="2"/>
-    </row>
-    <row r="85" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="2"/>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="19"/>
-      <c r="E85" s="19"/>
-      <c r="F85" s="20"/>
-      <c r="H85" s="6"/>
-      <c r="I85" s="6"/>
-      <c r="J85" s="6"/>
-      <c r="K85" s="6"/>
-      <c r="L85" s="6"/>
-      <c r="M85" s="6"/>
-      <c r="N85" s="6"/>
-      <c r="O85" s="6"/>
-      <c r="P85" s="6"/>
-      <c r="Q85" s="6"/>
-      <c r="R85" s="6"/>
-      <c r="S85" s="6"/>
-      <c r="T85" s="6"/>
-      <c r="U85" s="6"/>
-      <c r="V85" s="6"/>
-      <c r="W85" s="6"/>
-      <c r="X85" s="6"/>
-      <c r="Y85" s="6"/>
-      <c r="Z85" s="6"/>
-      <c r="AA85" s="6"/>
-      <c r="AB85" s="6"/>
-      <c r="AC85" s="6"/>
-      <c r="AD85" s="6"/>
-      <c r="AE85" s="6"/>
-      <c r="AF85" s="6"/>
-      <c r="AG85" s="6"/>
-      <c r="AH85" s="6"/>
-      <c r="AI85" s="6"/>
-      <c r="AJ85" s="6"/>
-      <c r="AK85" s="6"/>
-      <c r="AL85" s="6"/>
-      <c r="AM85" s="2"/>
-      <c r="AN85" s="2"/>
-      <c r="AO85" s="2"/>
-      <c r="AP85" s="2"/>
-      <c r="AQ85" s="2"/>
-      <c r="AR85" s="2"/>
-      <c r="AS85" s="2"/>
-      <c r="AT85" s="2"/>
-      <c r="AU85" s="2"/>
-      <c r="AV85" s="2"/>
-      <c r="AW85" s="2"/>
-      <c r="AX85" s="2"/>
-      <c r="AY85" s="2"/>
-      <c r="AZ85" s="2"/>
-      <c r="BA85" s="2"/>
-      <c r="BB85" s="2"/>
-      <c r="BC85" s="2"/>
-      <c r="BD85" s="2"/>
-      <c r="BE85" s="2"/>
-      <c r="BF85" s="2"/>
-      <c r="BG85" s="2"/>
-      <c r="BH85" s="2"/>
-      <c r="BI85" s="2"/>
-      <c r="BJ85" s="2"/>
-      <c r="BK85" s="2"/>
-      <c r="BL85" s="2"/>
-      <c r="BM85" s="2"/>
-      <c r="BN85" s="2"/>
-      <c r="BO85" s="2"/>
-      <c r="BP85" s="2"/>
-    </row>
-    <row r="86" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="2"/>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="19"/>
-      <c r="E86" s="19"/>
-      <c r="F86" s="20"/>
-      <c r="H86" s="6"/>
-      <c r="I86" s="6"/>
-      <c r="J86" s="6"/>
-      <c r="K86" s="6"/>
-      <c r="L86" s="6"/>
-      <c r="M86" s="6"/>
-      <c r="N86" s="6"/>
-      <c r="O86" s="6"/>
-      <c r="P86" s="6"/>
-      <c r="Q86" s="6"/>
-      <c r="R86" s="6"/>
-      <c r="S86" s="6"/>
-      <c r="T86" s="6"/>
-      <c r="U86" s="6"/>
-      <c r="V86" s="6"/>
-      <c r="W86" s="6"/>
-      <c r="X86" s="6"/>
-      <c r="Y86" s="6"/>
-      <c r="Z86" s="6"/>
-      <c r="AA86" s="6"/>
-      <c r="AB86" s="6"/>
-      <c r="AC86" s="6"/>
-      <c r="AD86" s="6"/>
-      <c r="AE86" s="6"/>
-      <c r="AF86" s="6"/>
-      <c r="AG86" s="6"/>
-      <c r="AH86" s="6"/>
-      <c r="AI86" s="6"/>
-      <c r="AJ86" s="6"/>
-      <c r="AK86" s="6"/>
-      <c r="AL86" s="6"/>
-      <c r="AM86" s="2"/>
-      <c r="AN86" s="2"/>
-      <c r="AO86" s="2"/>
-      <c r="AP86" s="2"/>
-      <c r="AQ86" s="2"/>
-      <c r="AR86" s="2"/>
-      <c r="AS86" s="2"/>
-      <c r="AT86" s="2"/>
-      <c r="AU86" s="2"/>
-      <c r="AV86" s="2"/>
-      <c r="AW86" s="2"/>
-      <c r="AX86" s="2"/>
-      <c r="AY86" s="2"/>
-      <c r="AZ86" s="2"/>
-      <c r="BA86" s="2"/>
-      <c r="BB86" s="2"/>
-      <c r="BC86" s="2"/>
-      <c r="BD86" s="2"/>
-      <c r="BE86" s="2"/>
-      <c r="BF86" s="2"/>
-      <c r="BG86" s="2"/>
-      <c r="BH86" s="2"/>
-      <c r="BI86" s="2"/>
-      <c r="BJ86" s="2"/>
-      <c r="BK86" s="2"/>
-      <c r="BL86" s="2"/>
-      <c r="BM86" s="2"/>
-      <c r="BN86" s="2"/>
-      <c r="BO86" s="2"/>
-      <c r="BP86" s="2"/>
-    </row>
-    <row r="87" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="2"/>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="19"/>
-      <c r="E87" s="19"/>
-      <c r="F87" s="20"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="6"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6"/>
-      <c r="L87" s="6"/>
-      <c r="M87" s="6"/>
-      <c r="N87" s="6"/>
-      <c r="O87" s="6"/>
-      <c r="P87" s="6"/>
-      <c r="Q87" s="6"/>
-      <c r="R87" s="6"/>
-      <c r="S87" s="6"/>
-      <c r="T87" s="6"/>
-      <c r="U87" s="6"/>
-      <c r="V87" s="6"/>
-      <c r="W87" s="6"/>
-      <c r="X87" s="6"/>
-      <c r="Y87" s="6"/>
-      <c r="Z87" s="6"/>
-      <c r="AA87" s="6"/>
-      <c r="AB87" s="6"/>
-      <c r="AC87" s="6"/>
-      <c r="AD87" s="6"/>
-      <c r="AE87" s="6"/>
-      <c r="AF87" s="6"/>
-      <c r="AG87" s="6"/>
-      <c r="AH87" s="6"/>
-      <c r="AI87" s="6"/>
-      <c r="AJ87" s="6"/>
-      <c r="AK87" s="6"/>
-      <c r="AL87" s="6"/>
-      <c r="AM87" s="2"/>
-      <c r="AN87" s="2"/>
-      <c r="AO87" s="2"/>
-      <c r="AP87" s="2"/>
-      <c r="AQ87" s="2"/>
-      <c r="AR87" s="2"/>
-      <c r="AS87" s="2"/>
-      <c r="AT87" s="2"/>
-      <c r="AU87" s="2"/>
-      <c r="AV87" s="2"/>
-      <c r="AW87" s="2"/>
-      <c r="AX87" s="2"/>
-      <c r="AY87" s="2"/>
-      <c r="AZ87" s="2"/>
-      <c r="BA87" s="2"/>
-      <c r="BB87" s="2"/>
-      <c r="BC87" s="2"/>
-      <c r="BD87" s="2"/>
-      <c r="BE87" s="2"/>
-      <c r="BF87" s="2"/>
-      <c r="BG87" s="2"/>
-      <c r="BH87" s="2"/>
-      <c r="BI87" s="2"/>
-      <c r="BJ87" s="2"/>
-      <c r="BK87" s="2"/>
-      <c r="BL87" s="2"/>
-      <c r="BM87" s="2"/>
-      <c r="BN87" s="2"/>
-      <c r="BO87" s="2"/>
-      <c r="BP87" s="2"/>
-    </row>
-    <row r="88" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="2"/>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="19"/>
-      <c r="E88" s="19"/>
-      <c r="F88" s="20"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-      <c r="J88" s="6"/>
-      <c r="K88" s="6"/>
-      <c r="L88" s="6"/>
-      <c r="M88" s="6"/>
-      <c r="N88" s="6"/>
-      <c r="O88" s="6"/>
-      <c r="P88" s="6"/>
-      <c r="Q88" s="6"/>
-      <c r="R88" s="6"/>
-      <c r="S88" s="6"/>
-      <c r="T88" s="6"/>
-      <c r="U88" s="6"/>
-      <c r="V88" s="6"/>
-      <c r="W88" s="6"/>
-      <c r="X88" s="6"/>
-      <c r="Y88" s="6"/>
-      <c r="Z88" s="6"/>
-      <c r="AA88" s="6"/>
-      <c r="AB88" s="6"/>
-      <c r="AC88" s="6"/>
-      <c r="AD88" s="6"/>
-      <c r="AE88" s="6"/>
-      <c r="AF88" s="6"/>
-      <c r="AG88" s="6"/>
-      <c r="AH88" s="6"/>
-      <c r="AI88" s="6"/>
-      <c r="AJ88" s="6"/>
-      <c r="AK88" s="6"/>
-      <c r="AL88" s="6"/>
-      <c r="AM88" s="2"/>
-      <c r="AN88" s="2"/>
-      <c r="AO88" s="2"/>
-      <c r="AP88" s="2"/>
-      <c r="AQ88" s="2"/>
-      <c r="AR88" s="2"/>
-      <c r="AS88" s="2"/>
-      <c r="AT88" s="2"/>
-      <c r="AU88" s="2"/>
-      <c r="AV88" s="2"/>
-      <c r="AW88" s="2"/>
-      <c r="AX88" s="2"/>
-      <c r="AY88" s="2"/>
-      <c r="AZ88" s="2"/>
-      <c r="BA88" s="2"/>
-      <c r="BB88" s="2"/>
-      <c r="BC88" s="2"/>
-      <c r="BD88" s="2"/>
-      <c r="BE88" s="2"/>
-      <c r="BF88" s="2"/>
-      <c r="BG88" s="2"/>
-      <c r="BH88" s="2"/>
-      <c r="BI88" s="2"/>
-      <c r="BJ88" s="2"/>
-      <c r="BK88" s="2"/>
-      <c r="BL88" s="2"/>
-      <c r="BM88" s="2"/>
-      <c r="BN88" s="2"/>
-      <c r="BO88" s="2"/>
-      <c r="BP88" s="2"/>
-    </row>
-    <row r="89" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="2"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="19"/>
-      <c r="E89" s="19"/>
-      <c r="F89" s="20"/>
-      <c r="H89" s="6"/>
-      <c r="I89" s="6"/>
-      <c r="J89" s="6"/>
-      <c r="K89" s="6"/>
-      <c r="L89" s="6"/>
-      <c r="M89" s="6"/>
-      <c r="N89" s="6"/>
-      <c r="O89" s="6"/>
-      <c r="P89" s="6"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="6"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="6"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="6"/>
-      <c r="AB89" s="6"/>
-      <c r="AC89" s="6"/>
-      <c r="AD89" s="6"/>
-      <c r="AE89" s="6"/>
-      <c r="AF89" s="6"/>
-      <c r="AG89" s="6"/>
-      <c r="AH89" s="6"/>
-      <c r="AI89" s="6"/>
-      <c r="AJ89" s="6"/>
-      <c r="AK89" s="6"/>
-      <c r="AL89" s="6"/>
-      <c r="AM89" s="2"/>
-      <c r="AN89" s="2"/>
-      <c r="AO89" s="2"/>
-      <c r="AP89" s="2"/>
-      <c r="AQ89" s="2"/>
-      <c r="AR89" s="2"/>
-      <c r="AS89" s="2"/>
-      <c r="AT89" s="2"/>
-      <c r="AU89" s="2"/>
-      <c r="AV89" s="2"/>
-      <c r="AW89" s="2"/>
-      <c r="AX89" s="2"/>
-      <c r="AY89" s="2"/>
-      <c r="AZ89" s="2"/>
-      <c r="BA89" s="2"/>
-      <c r="BB89" s="2"/>
-      <c r="BC89" s="2"/>
-      <c r="BD89" s="2"/>
-      <c r="BE89" s="2"/>
-      <c r="BF89" s="2"/>
-      <c r="BG89" s="2"/>
-      <c r="BH89" s="2"/>
-      <c r="BI89" s="2"/>
-      <c r="BJ89" s="2"/>
-      <c r="BK89" s="2"/>
-      <c r="BL89" s="2"/>
-      <c r="BM89" s="2"/>
-      <c r="BN89" s="2"/>
-      <c r="BO89" s="2"/>
-      <c r="BP89" s="2"/>
-    </row>
-    <row r="90" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="2"/>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="19"/>
-      <c r="E90" s="19"/>
-      <c r="F90" s="20"/>
-      <c r="H90" s="6"/>
-      <c r="I90" s="6"/>
-      <c r="J90" s="6"/>
-      <c r="K90" s="6"/>
-      <c r="L90" s="6"/>
-      <c r="M90" s="6"/>
-      <c r="N90" s="6"/>
-      <c r="O90" s="6"/>
-      <c r="P90" s="6"/>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="6"/>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
-      <c r="V90" s="6"/>
-      <c r="W90" s="6"/>
-      <c r="X90" s="6"/>
-      <c r="Y90" s="6"/>
-      <c r="Z90" s="6"/>
-      <c r="AA90" s="6"/>
-      <c r="AB90" s="6"/>
-      <c r="AC90" s="6"/>
-      <c r="AD90" s="6"/>
-      <c r="AE90" s="6"/>
-      <c r="AF90" s="6"/>
-      <c r="AG90" s="6"/>
-      <c r="AH90" s="6"/>
-      <c r="AI90" s="6"/>
-      <c r="AJ90" s="6"/>
-      <c r="AK90" s="6"/>
-      <c r="AL90" s="6"/>
-      <c r="AM90" s="2"/>
-      <c r="AN90" s="2"/>
-      <c r="AO90" s="2"/>
-      <c r="AP90" s="2"/>
-      <c r="AQ90" s="2"/>
-      <c r="AR90" s="2"/>
-      <c r="AS90" s="2"/>
-      <c r="AT90" s="2"/>
-      <c r="AU90" s="2"/>
-      <c r="AV90" s="2"/>
-      <c r="AW90" s="2"/>
-      <c r="AX90" s="2"/>
-      <c r="AY90" s="2"/>
-      <c r="AZ90" s="2"/>
-      <c r="BA90" s="2"/>
-      <c r="BB90" s="2"/>
-      <c r="BC90" s="2"/>
-      <c r="BD90" s="2"/>
-      <c r="BE90" s="2"/>
-      <c r="BF90" s="2"/>
-      <c r="BG90" s="2"/>
-      <c r="BH90" s="2"/>
-      <c r="BI90" s="2"/>
-      <c r="BJ90" s="2"/>
-      <c r="BK90" s="2"/>
-      <c r="BL90" s="2"/>
-      <c r="BM90" s="2"/>
-      <c r="BN90" s="2"/>
-      <c r="BO90" s="2"/>
-      <c r="BP90" s="2"/>
-    </row>
-    <row r="91" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="2"/>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="19"/>
-      <c r="E91" s="19"/>
-      <c r="F91" s="20"/>
-      <c r="H91" s="6"/>
-      <c r="I91" s="6"/>
-      <c r="J91" s="6"/>
-      <c r="K91" s="6"/>
-      <c r="L91" s="6"/>
-      <c r="M91" s="6"/>
-      <c r="N91" s="6"/>
-      <c r="O91" s="6"/>
-      <c r="P91" s="6"/>
-      <c r="Q91" s="6"/>
-      <c r="R91" s="6"/>
-      <c r="S91" s="6"/>
-      <c r="T91" s="6"/>
-      <c r="U91" s="6"/>
-      <c r="V91" s="6"/>
-      <c r="W91" s="6"/>
-      <c r="X91" s="6"/>
-      <c r="Y91" s="6"/>
-      <c r="Z91" s="6"/>
-      <c r="AA91" s="6"/>
-      <c r="AB91" s="6"/>
-      <c r="AC91" s="6"/>
-      <c r="AD91" s="6"/>
-      <c r="AE91" s="6"/>
-      <c r="AF91" s="6"/>
-      <c r="AG91" s="6"/>
-      <c r="AH91" s="6"/>
-      <c r="AI91" s="6"/>
-      <c r="AJ91" s="6"/>
-      <c r="AK91" s="6"/>
-      <c r="AL91" s="6"/>
-      <c r="AM91" s="2"/>
-      <c r="AN91" s="2"/>
-      <c r="AO91" s="2"/>
-      <c r="AP91" s="2"/>
-      <c r="AQ91" s="2"/>
-      <c r="AR91" s="2"/>
-      <c r="AS91" s="2"/>
-      <c r="AT91" s="2"/>
-      <c r="AU91" s="2"/>
-      <c r="AV91" s="2"/>
-      <c r="AW91" s="2"/>
-      <c r="AX91" s="2"/>
-      <c r="AY91" s="2"/>
-      <c r="AZ91" s="2"/>
-      <c r="BA91" s="2"/>
-      <c r="BB91" s="2"/>
-      <c r="BC91" s="2"/>
-      <c r="BD91" s="2"/>
-      <c r="BE91" s="2"/>
-      <c r="BF91" s="2"/>
-      <c r="BG91" s="2"/>
-      <c r="BH91" s="2"/>
-      <c r="BI91" s="2"/>
-      <c r="BJ91" s="2"/>
-      <c r="BK91" s="2"/>
-      <c r="BL91" s="2"/>
-      <c r="BM91" s="2"/>
-      <c r="BN91" s="2"/>
-      <c r="BO91" s="2"/>
-      <c r="BP91" s="2"/>
-    </row>
-    <row r="92" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="2"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="19"/>
-      <c r="E92" s="19"/>
-      <c r="F92" s="20"/>
-      <c r="H92" s="6"/>
-      <c r="I92" s="6"/>
-      <c r="J92" s="6"/>
-      <c r="K92" s="6"/>
-      <c r="L92" s="6"/>
-      <c r="M92" s="6"/>
-      <c r="N92" s="6"/>
-      <c r="O92" s="6"/>
-      <c r="P92" s="6"/>
-      <c r="Q92" s="6"/>
-      <c r="R92" s="6"/>
-      <c r="S92" s="6"/>
-      <c r="T92" s="6"/>
-      <c r="U92" s="6"/>
-      <c r="V92" s="6"/>
-      <c r="W92" s="6"/>
-      <c r="X92" s="6"/>
-      <c r="Y92" s="6"/>
-      <c r="Z92" s="6"/>
-      <c r="AA92" s="6"/>
-      <c r="AB92" s="6"/>
-      <c r="AC92" s="6"/>
-      <c r="AD92" s="6"/>
-      <c r="AE92" s="6"/>
-      <c r="AF92" s="6"/>
-      <c r="AG92" s="6"/>
-      <c r="AH92" s="6"/>
-      <c r="AI92" s="6"/>
-      <c r="AJ92" s="6"/>
-      <c r="AK92" s="6"/>
-      <c r="AL92" s="6"/>
-      <c r="AM92" s="2"/>
-      <c r="AN92" s="2"/>
-      <c r="AO92" s="2"/>
-      <c r="AP92" s="2"/>
-      <c r="AQ92" s="2"/>
-      <c r="AR92" s="2"/>
-      <c r="AS92" s="2"/>
-      <c r="AT92" s="2"/>
-      <c r="AU92" s="2"/>
-      <c r="AV92" s="2"/>
-      <c r="AW92" s="2"/>
-      <c r="AX92" s="2"/>
-      <c r="AY92" s="2"/>
-      <c r="AZ92" s="2"/>
-      <c r="BA92" s="2"/>
-      <c r="BB92" s="2"/>
-      <c r="BC92" s="2"/>
-      <c r="BD92" s="2"/>
-      <c r="BE92" s="2"/>
-      <c r="BF92" s="2"/>
-      <c r="BG92" s="2"/>
-      <c r="BH92" s="2"/>
-      <c r="BI92" s="2"/>
-      <c r="BJ92" s="2"/>
-      <c r="BK92" s="2"/>
-      <c r="BL92" s="2"/>
-      <c r="BM92" s="2"/>
-      <c r="BN92" s="2"/>
-      <c r="BO92" s="2"/>
-      <c r="BP92" s="2"/>
-    </row>
-    <row r="93" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="2"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="19"/>
-      <c r="E93" s="19"/>
-      <c r="F93" s="20"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="6"/>
-      <c r="J93" s="6"/>
-      <c r="K93" s="6"/>
-      <c r="L93" s="6"/>
-      <c r="M93" s="6"/>
-      <c r="N93" s="6"/>
-      <c r="O93" s="6"/>
-      <c r="P93" s="6"/>
-      <c r="Q93" s="6"/>
-      <c r="R93" s="6"/>
-      <c r="S93" s="6"/>
-      <c r="T93" s="6"/>
-      <c r="U93" s="6"/>
-      <c r="V93" s="6"/>
-      <c r="W93" s="6"/>
-      <c r="X93" s="6"/>
-      <c r="Y93" s="6"/>
-      <c r="Z93" s="6"/>
-      <c r="AA93" s="6"/>
-      <c r="AB93" s="6"/>
-      <c r="AC93" s="6"/>
-      <c r="AD93" s="6"/>
-      <c r="AE93" s="6"/>
-      <c r="AF93" s="6"/>
-      <c r="AG93" s="6"/>
-      <c r="AH93" s="6"/>
-      <c r="AI93" s="6"/>
-      <c r="AJ93" s="6"/>
-      <c r="AK93" s="6"/>
-      <c r="AL93" s="6"/>
-      <c r="AM93" s="2"/>
-      <c r="AN93" s="2"/>
-      <c r="AO93" s="2"/>
-      <c r="AP93" s="2"/>
-      <c r="AQ93" s="2"/>
-      <c r="AR93" s="2"/>
-      <c r="AS93" s="2"/>
-      <c r="AT93" s="2"/>
-      <c r="AU93" s="2"/>
-      <c r="AV93" s="2"/>
-      <c r="AW93" s="2"/>
-      <c r="AX93" s="2"/>
-      <c r="AY93" s="2"/>
-      <c r="AZ93" s="2"/>
-      <c r="BA93" s="2"/>
-      <c r="BB93" s="2"/>
-      <c r="BC93" s="2"/>
-      <c r="BD93" s="2"/>
-      <c r="BE93" s="2"/>
-      <c r="BF93" s="2"/>
-      <c r="BG93" s="2"/>
-      <c r="BH93" s="2"/>
-      <c r="BI93" s="2"/>
-      <c r="BJ93" s="2"/>
-      <c r="BK93" s="2"/>
-      <c r="BL93" s="2"/>
-      <c r="BM93" s="2"/>
-      <c r="BN93" s="2"/>
-      <c r="BO93" s="2"/>
-      <c r="BP93" s="2"/>
-    </row>
-    <row r="94" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="2"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="19"/>
-      <c r="E94" s="19"/>
-      <c r="F94" s="20"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="6"/>
-      <c r="L94" s="6"/>
-      <c r="M94" s="6"/>
-      <c r="N94" s="6"/>
-      <c r="O94" s="6"/>
-      <c r="P94" s="6"/>
-      <c r="Q94" s="6"/>
-      <c r="R94" s="6"/>
-      <c r="S94" s="6"/>
-      <c r="T94" s="6"/>
-      <c r="U94" s="6"/>
-      <c r="V94" s="6"/>
-      <c r="W94" s="6"/>
-      <c r="X94" s="6"/>
-      <c r="Y94" s="6"/>
-      <c r="Z94" s="6"/>
-      <c r="AA94" s="6"/>
-      <c r="AB94" s="6"/>
-      <c r="AC94" s="6"/>
-      <c r="AD94" s="6"/>
-      <c r="AE94" s="6"/>
-      <c r="AF94" s="6"/>
-      <c r="AG94" s="6"/>
-      <c r="AH94" s="6"/>
-      <c r="AI94" s="6"/>
-      <c r="AJ94" s="6"/>
-      <c r="AK94" s="6"/>
-      <c r="AL94" s="6"/>
-      <c r="AM94" s="2"/>
-      <c r="AN94" s="2"/>
-      <c r="AO94" s="2"/>
-      <c r="AP94" s="2"/>
-      <c r="AQ94" s="2"/>
-      <c r="AR94" s="2"/>
-      <c r="AS94" s="2"/>
-      <c r="AT94" s="2"/>
-      <c r="AU94" s="2"/>
-      <c r="AV94" s="2"/>
-      <c r="AW94" s="2"/>
-      <c r="AX94" s="2"/>
-      <c r="AY94" s="2"/>
-      <c r="AZ94" s="2"/>
-      <c r="BA94" s="2"/>
-      <c r="BB94" s="2"/>
-      <c r="BC94" s="2"/>
-      <c r="BD94" s="2"/>
-      <c r="BE94" s="2"/>
-      <c r="BF94" s="2"/>
-      <c r="BG94" s="2"/>
-      <c r="BH94" s="2"/>
-      <c r="BI94" s="2"/>
-      <c r="BJ94" s="2"/>
-      <c r="BK94" s="2"/>
-      <c r="BL94" s="2"/>
-      <c r="BM94" s="2"/>
-      <c r="BN94" s="2"/>
-      <c r="BO94" s="2"/>
-      <c r="BP94" s="2"/>
-    </row>
-    <row r="95" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="2"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="19"/>
-      <c r="E95" s="19"/>
-      <c r="F95" s="20"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="6"/>
-      <c r="J95" s="6"/>
-      <c r="K95" s="6"/>
-      <c r="L95" s="6"/>
-      <c r="M95" s="6"/>
-      <c r="N95" s="6"/>
-      <c r="O95" s="6"/>
-      <c r="P95" s="6"/>
-      <c r="Q95" s="6"/>
-      <c r="R95" s="6"/>
-      <c r="S95" s="6"/>
-      <c r="T95" s="6"/>
-      <c r="U95" s="6"/>
-      <c r="V95" s="6"/>
-      <c r="W95" s="6"/>
-      <c r="X95" s="6"/>
-      <c r="Y95" s="6"/>
-      <c r="Z95" s="6"/>
-      <c r="AA95" s="6"/>
-      <c r="AB95" s="6"/>
-      <c r="AC95" s="6"/>
-      <c r="AD95" s="6"/>
-      <c r="AE95" s="6"/>
-      <c r="AF95" s="6"/>
-      <c r="AG95" s="6"/>
-      <c r="AH95" s="6"/>
-      <c r="AI95" s="6"/>
-      <c r="AJ95" s="6"/>
-      <c r="AK95" s="6"/>
-      <c r="AL95" s="6"/>
-      <c r="AM95" s="2"/>
-      <c r="AN95" s="2"/>
-      <c r="AO95" s="2"/>
-      <c r="AP95" s="2"/>
-      <c r="AQ95" s="2"/>
-      <c r="AR95" s="2"/>
-      <c r="AS95" s="2"/>
-      <c r="AT95" s="2"/>
-      <c r="AU95" s="2"/>
-      <c r="AV95" s="2"/>
-      <c r="AW95" s="2"/>
-      <c r="AX95" s="2"/>
-      <c r="AY95" s="2"/>
-      <c r="AZ95" s="2"/>
-      <c r="BA95" s="2"/>
-      <c r="BB95" s="2"/>
-      <c r="BC95" s="2"/>
-      <c r="BD95" s="2"/>
-      <c r="BE95" s="2"/>
-      <c r="BF95" s="2"/>
-      <c r="BG95" s="2"/>
-      <c r="BH95" s="2"/>
-      <c r="BI95" s="2"/>
-      <c r="BJ95" s="2"/>
-      <c r="BK95" s="2"/>
-      <c r="BL95" s="2"/>
-      <c r="BM95" s="2"/>
-      <c r="BN95" s="2"/>
-      <c r="BO95" s="2"/>
-      <c r="BP95" s="2"/>
-    </row>
-    <row r="96" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="2"/>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="19"/>
-      <c r="E96" s="19"/>
-      <c r="F96" s="20"/>
-      <c r="H96" s="6"/>
-      <c r="I96" s="6"/>
-      <c r="J96" s="6"/>
-      <c r="K96" s="6"/>
-      <c r="L96" s="6"/>
-      <c r="M96" s="6"/>
-      <c r="N96" s="6"/>
-      <c r="O96" s="6"/>
-      <c r="P96" s="6"/>
-      <c r="Q96" s="6"/>
-      <c r="R96" s="6"/>
-      <c r="S96" s="6"/>
-      <c r="T96" s="6"/>
-      <c r="U96" s="6"/>
-      <c r="V96" s="6"/>
-      <c r="W96" s="6"/>
-      <c r="X96" s="6"/>
-      <c r="Y96" s="6"/>
-      <c r="Z96" s="6"/>
-      <c r="AA96" s="6"/>
-      <c r="AB96" s="6"/>
-      <c r="AC96" s="6"/>
-      <c r="AD96" s="6"/>
-      <c r="AE96" s="6"/>
-      <c r="AF96" s="6"/>
-      <c r="AG96" s="6"/>
-      <c r="AH96" s="6"/>
-      <c r="AI96" s="6"/>
-      <c r="AJ96" s="6"/>
-      <c r="AK96" s="6"/>
-      <c r="AL96" s="6"/>
-      <c r="AM96" s="2"/>
-      <c r="AN96" s="2"/>
-      <c r="AO96" s="2"/>
-      <c r="AP96" s="2"/>
-      <c r="AQ96" s="2"/>
-      <c r="AR96" s="2"/>
-      <c r="AS96" s="2"/>
-      <c r="AT96" s="2"/>
-      <c r="AU96" s="2"/>
-      <c r="AV96" s="2"/>
-      <c r="AW96" s="2"/>
-      <c r="AX96" s="2"/>
-      <c r="AY96" s="2"/>
-      <c r="AZ96" s="2"/>
-      <c r="BA96" s="2"/>
-      <c r="BB96" s="2"/>
-      <c r="BC96" s="2"/>
-      <c r="BD96" s="2"/>
-      <c r="BE96" s="2"/>
-      <c r="BF96" s="2"/>
-      <c r="BG96" s="2"/>
-      <c r="BH96" s="2"/>
-      <c r="BI96" s="2"/>
-      <c r="BJ96" s="2"/>
-      <c r="BK96" s="2"/>
-      <c r="BL96" s="2"/>
-      <c r="BM96" s="2"/>
-      <c r="BN96" s="2"/>
-      <c r="BO96" s="2"/>
-      <c r="BP96" s="2"/>
-    </row>
-    <row r="97" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="2"/>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="19"/>
-      <c r="E97" s="19"/>
-      <c r="F97" s="20"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="6"/>
-      <c r="J97" s="6"/>
-      <c r="K97" s="6"/>
-      <c r="L97" s="6"/>
-      <c r="M97" s="6"/>
-      <c r="N97" s="6"/>
-      <c r="O97" s="6"/>
-      <c r="P97" s="6"/>
-      <c r="Q97" s="6"/>
-      <c r="R97" s="6"/>
-      <c r="S97" s="6"/>
-      <c r="T97" s="6"/>
-      <c r="U97" s="6"/>
-      <c r="V97" s="6"/>
-      <c r="W97" s="6"/>
-      <c r="X97" s="6"/>
-      <c r="Y97" s="6"/>
-      <c r="Z97" s="6"/>
-      <c r="AA97" s="6"/>
-      <c r="AB97" s="6"/>
-      <c r="AC97" s="6"/>
-      <c r="AD97" s="6"/>
-      <c r="AE97" s="6"/>
-      <c r="AF97" s="6"/>
-      <c r="AG97" s="6"/>
-      <c r="AH97" s="6"/>
-      <c r="AI97" s="6"/>
-      <c r="AJ97" s="6"/>
-      <c r="AK97" s="6"/>
-      <c r="AL97" s="6"/>
-      <c r="AM97" s="2"/>
-      <c r="AN97" s="2"/>
-      <c r="AO97" s="2"/>
-      <c r="AP97" s="2"/>
-      <c r="AQ97" s="2"/>
-      <c r="AR97" s="2"/>
-      <c r="AS97" s="2"/>
-      <c r="AT97" s="2"/>
-      <c r="AU97" s="2"/>
-      <c r="AV97" s="2"/>
-      <c r="AW97" s="2"/>
-      <c r="AX97" s="2"/>
-      <c r="AY97" s="2"/>
-      <c r="AZ97" s="2"/>
-      <c r="BA97" s="2"/>
-      <c r="BB97" s="2"/>
-      <c r="BC97" s="2"/>
-      <c r="BD97" s="2"/>
-      <c r="BE97" s="2"/>
-      <c r="BF97" s="2"/>
-      <c r="BG97" s="2"/>
-      <c r="BH97" s="2"/>
-      <c r="BI97" s="2"/>
-      <c r="BJ97" s="2"/>
-      <c r="BK97" s="2"/>
-      <c r="BL97" s="2"/>
-      <c r="BM97" s="2"/>
-      <c r="BN97" s="2"/>
-      <c r="BO97" s="2"/>
-      <c r="BP97" s="2"/>
-    </row>
-    <row r="98" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="2"/>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="19"/>
-      <c r="E98" s="19"/>
-      <c r="F98" s="20"/>
-      <c r="H98" s="6"/>
-      <c r="I98" s="6"/>
-      <c r="J98" s="6"/>
-      <c r="K98" s="6"/>
-      <c r="L98" s="6"/>
-      <c r="M98" s="6"/>
-      <c r="N98" s="6"/>
-      <c r="O98" s="6"/>
-      <c r="P98" s="6"/>
-      <c r="Q98" s="6"/>
-      <c r="R98" s="6"/>
-      <c r="S98" s="6"/>
-      <c r="T98" s="6"/>
-      <c r="U98" s="6"/>
-      <c r="V98" s="6"/>
-      <c r="W98" s="6"/>
-      <c r="X98" s="6"/>
-      <c r="Y98" s="6"/>
-      <c r="Z98" s="6"/>
-      <c r="AA98" s="6"/>
-      <c r="AB98" s="6"/>
-      <c r="AC98" s="6"/>
-      <c r="AD98" s="6"/>
-      <c r="AE98" s="6"/>
-      <c r="AF98" s="6"/>
-      <c r="AG98" s="6"/>
-      <c r="AH98" s="6"/>
-      <c r="AI98" s="6"/>
-      <c r="AJ98" s="6"/>
-      <c r="AK98" s="6"/>
-      <c r="AL98" s="6"/>
-      <c r="AM98" s="2"/>
-      <c r="AN98" s="2"/>
-      <c r="AO98" s="2"/>
-      <c r="AP98" s="2"/>
-      <c r="AQ98" s="2"/>
-      <c r="AR98" s="2"/>
-      <c r="AS98" s="2"/>
-      <c r="AT98" s="2"/>
-      <c r="AU98" s="2"/>
-      <c r="AV98" s="2"/>
-      <c r="AW98" s="2"/>
-      <c r="AX98" s="2"/>
-      <c r="AY98" s="2"/>
-      <c r="AZ98" s="2"/>
-      <c r="BA98" s="2"/>
-      <c r="BB98" s="2"/>
-      <c r="BC98" s="2"/>
-      <c r="BD98" s="2"/>
-      <c r="BE98" s="2"/>
-      <c r="BF98" s="2"/>
-      <c r="BG98" s="2"/>
-      <c r="BH98" s="2"/>
-      <c r="BI98" s="2"/>
-      <c r="BJ98" s="2"/>
-      <c r="BK98" s="2"/>
-      <c r="BL98" s="2"/>
-      <c r="BM98" s="2"/>
-      <c r="BN98" s="2"/>
-      <c r="BO98" s="2"/>
-      <c r="BP98" s="2"/>
-    </row>
-    <row r="99" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="2"/>
-      <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="19"/>
-      <c r="E99" s="19"/>
-      <c r="F99" s="20"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="6"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="6"/>
-      <c r="L99" s="6"/>
-      <c r="M99" s="6"/>
-      <c r="N99" s="6"/>
-      <c r="O99" s="6"/>
-      <c r="P99" s="6"/>
-      <c r="Q99" s="6"/>
-      <c r="R99" s="6"/>
-      <c r="S99" s="6"/>
-      <c r="T99" s="6"/>
-      <c r="U99" s="6"/>
-      <c r="V99" s="6"/>
-      <c r="W99" s="6"/>
-      <c r="X99" s="6"/>
-      <c r="Y99" s="6"/>
-      <c r="Z99" s="6"/>
-      <c r="AA99" s="6"/>
-      <c r="AB99" s="6"/>
-      <c r="AC99" s="6"/>
-      <c r="AD99" s="6"/>
-      <c r="AE99" s="6"/>
-      <c r="AF99" s="6"/>
-      <c r="AG99" s="6"/>
-      <c r="AH99" s="6"/>
-      <c r="AI99" s="6"/>
-      <c r="AJ99" s="6"/>
-      <c r="AK99" s="6"/>
-      <c r="AL99" s="6"/>
-      <c r="AM99" s="2"/>
-      <c r="AN99" s="2"/>
-      <c r="AO99" s="2"/>
-      <c r="AP99" s="2"/>
-      <c r="AQ99" s="2"/>
-      <c r="AR99" s="2"/>
-      <c r="AS99" s="2"/>
-      <c r="AT99" s="2"/>
-      <c r="AU99" s="2"/>
-      <c r="AV99" s="2"/>
-      <c r="AW99" s="2"/>
-      <c r="AX99" s="2"/>
-      <c r="AY99" s="2"/>
-      <c r="AZ99" s="2"/>
-      <c r="BA99" s="2"/>
-      <c r="BB99" s="2"/>
-      <c r="BC99" s="2"/>
-      <c r="BD99" s="2"/>
-      <c r="BE99" s="2"/>
-      <c r="BF99" s="2"/>
-      <c r="BG99" s="2"/>
-      <c r="BH99" s="2"/>
-      <c r="BI99" s="2"/>
-      <c r="BJ99" s="2"/>
-      <c r="BK99" s="2"/>
-      <c r="BL99" s="2"/>
-      <c r="BM99" s="2"/>
-      <c r="BN99" s="2"/>
-      <c r="BO99" s="2"/>
-      <c r="BP99" s="2"/>
-    </row>
-    <row r="100" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="2"/>
-      <c r="B100" s="4"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="19"/>
-      <c r="E100" s="19"/>
-      <c r="F100" s="20"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="6"/>
-      <c r="L100" s="6"/>
-      <c r="M100" s="6"/>
-      <c r="N100" s="6"/>
-      <c r="O100" s="6"/>
-      <c r="P100" s="6"/>
-      <c r="Q100" s="6"/>
-      <c r="R100" s="6"/>
-      <c r="S100" s="6"/>
-      <c r="T100" s="6"/>
-      <c r="U100" s="6"/>
-      <c r="V100" s="6"/>
-      <c r="W100" s="6"/>
-      <c r="X100" s="6"/>
-      <c r="Y100" s="6"/>
-      <c r="Z100" s="6"/>
-      <c r="AA100" s="6"/>
-      <c r="AB100" s="6"/>
-      <c r="AC100" s="6"/>
-      <c r="AD100" s="6"/>
-      <c r="AE100" s="6"/>
-      <c r="AF100" s="6"/>
-      <c r="AG100" s="6"/>
-      <c r="AH100" s="6"/>
-      <c r="AI100" s="6"/>
-      <c r="AJ100" s="6"/>
-      <c r="AK100" s="6"/>
-      <c r="AL100" s="6"/>
-      <c r="AM100" s="2"/>
-      <c r="AN100" s="2"/>
-      <c r="AO100" s="2"/>
-      <c r="AP100" s="2"/>
-      <c r="AQ100" s="2"/>
-      <c r="AR100" s="2"/>
-      <c r="AS100" s="2"/>
-      <c r="AT100" s="2"/>
-      <c r="AU100" s="2"/>
-      <c r="AV100" s="2"/>
-      <c r="AW100" s="2"/>
-      <c r="AX100" s="2"/>
-      <c r="AY100" s="2"/>
-      <c r="AZ100" s="2"/>
-      <c r="BA100" s="2"/>
-      <c r="BB100" s="2"/>
-      <c r="BC100" s="2"/>
-      <c r="BD100" s="2"/>
-      <c r="BE100" s="2"/>
-      <c r="BF100" s="2"/>
-      <c r="BG100" s="2"/>
-      <c r="BH100" s="2"/>
-      <c r="BI100" s="2"/>
-      <c r="BJ100" s="2"/>
-      <c r="BK100" s="2"/>
-      <c r="BL100" s="2"/>
-      <c r="BM100" s="2"/>
-      <c r="BN100" s="2"/>
-      <c r="BO100" s="2"/>
-      <c r="BP100" s="2"/>
-    </row>
-    <row r="101" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="2"/>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="19"/>
-      <c r="E101" s="19"/>
-      <c r="F101" s="20"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
-      <c r="J101" s="6"/>
-      <c r="K101" s="6"/>
-      <c r="L101" s="6"/>
-      <c r="M101" s="6"/>
-      <c r="N101" s="6"/>
-      <c r="O101" s="6"/>
-      <c r="P101" s="6"/>
-      <c r="Q101" s="6"/>
-      <c r="R101" s="6"/>
-      <c r="S101" s="6"/>
-      <c r="T101" s="6"/>
-      <c r="U101" s="6"/>
-      <c r="V101" s="6"/>
-      <c r="W101" s="6"/>
-      <c r="X101" s="6"/>
-      <c r="Y101" s="6"/>
-      <c r="Z101" s="6"/>
-      <c r="AA101" s="6"/>
-      <c r="AB101" s="6"/>
-      <c r="AC101" s="6"/>
-      <c r="AD101" s="6"/>
-      <c r="AE101" s="6"/>
-      <c r="AF101" s="6"/>
-      <c r="AG101" s="6"/>
-      <c r="AH101" s="6"/>
-      <c r="AI101" s="6"/>
-      <c r="AJ101" s="6"/>
-      <c r="AK101" s="6"/>
-      <c r="AL101" s="6"/>
-      <c r="AM101" s="2"/>
-      <c r="AN101" s="2"/>
-      <c r="AO101" s="2"/>
-      <c r="AP101" s="2"/>
-      <c r="AQ101" s="2"/>
-      <c r="AR101" s="2"/>
-      <c r="AS101" s="2"/>
-      <c r="AT101" s="2"/>
-      <c r="AU101" s="2"/>
-      <c r="AV101" s="2"/>
-      <c r="AW101" s="2"/>
-      <c r="AX101" s="2"/>
-      <c r="AY101" s="2"/>
-      <c r="AZ101" s="2"/>
-      <c r="BA101" s="2"/>
-      <c r="BB101" s="2"/>
-      <c r="BC101" s="2"/>
-      <c r="BD101" s="2"/>
-      <c r="BE101" s="2"/>
-      <c r="BF101" s="2"/>
-      <c r="BG101" s="2"/>
-      <c r="BH101" s="2"/>
-      <c r="BI101" s="2"/>
-      <c r="BJ101" s="2"/>
-      <c r="BK101" s="2"/>
-      <c r="BL101" s="2"/>
-      <c r="BM101" s="2"/>
-      <c r="BN101" s="2"/>
-      <c r="BO101" s="2"/>
-      <c r="BP101" s="2"/>
-    </row>
-    <row r="102" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="2"/>
-      <c r="B102" s="4"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="19"/>
-      <c r="E102" s="19"/>
-      <c r="F102" s="20"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6"/>
-      <c r="J102" s="6"/>
-      <c r="K102" s="6"/>
-      <c r="L102" s="6"/>
-      <c r="M102" s="6"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="6"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="6"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="6"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="6"/>
-      <c r="AB102" s="6"/>
-      <c r="AC102" s="6"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="2"/>
-      <c r="AN102" s="2"/>
-      <c r="AO102" s="2"/>
-      <c r="AP102" s="2"/>
-      <c r="AQ102" s="2"/>
-      <c r="AR102" s="2"/>
-      <c r="AS102" s="2"/>
-      <c r="AT102" s="2"/>
-      <c r="AU102" s="2"/>
-      <c r="AV102" s="2"/>
-      <c r="AW102" s="2"/>
-      <c r="AX102" s="2"/>
-      <c r="AY102" s="2"/>
-      <c r="AZ102" s="2"/>
-      <c r="BA102" s="2"/>
-      <c r="BB102" s="2"/>
-      <c r="BC102" s="2"/>
-      <c r="BD102" s="2"/>
-      <c r="BE102" s="2"/>
-      <c r="BF102" s="2"/>
-      <c r="BG102" s="2"/>
-      <c r="BH102" s="2"/>
-      <c r="BI102" s="2"/>
-      <c r="BJ102" s="2"/>
-      <c r="BK102" s="2"/>
-      <c r="BL102" s="2"/>
-      <c r="BM102" s="2"/>
-      <c r="BN102" s="2"/>
-      <c r="BO102" s="2"/>
-      <c r="BP102" s="2"/>
-    </row>
-    <row r="103" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="2"/>
-      <c r="B103" s="4"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="19"/>
-      <c r="E103" s="19"/>
-      <c r="F103" s="20"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="6"/>
-      <c r="J103" s="6"/>
-      <c r="K103" s="6"/>
-      <c r="L103" s="6"/>
-      <c r="M103" s="6"/>
-      <c r="N103" s="6"/>
-      <c r="O103" s="6"/>
-      <c r="P103" s="6"/>
-      <c r="Q103" s="6"/>
-      <c r="R103" s="6"/>
-      <c r="S103" s="6"/>
-      <c r="T103" s="6"/>
-      <c r="U103" s="6"/>
-      <c r="V103" s="6"/>
-      <c r="W103" s="6"/>
-      <c r="X103" s="6"/>
-      <c r="Y103" s="6"/>
-      <c r="Z103" s="6"/>
-      <c r="AA103" s="6"/>
-      <c r="AB103" s="6"/>
-      <c r="AC103" s="6"/>
-      <c r="AD103" s="6"/>
-      <c r="AE103" s="6"/>
-      <c r="AF103" s="6"/>
-      <c r="AG103" s="6"/>
-      <c r="AH103" s="6"/>
-      <c r="AI103" s="6"/>
-      <c r="AJ103" s="6"/>
-      <c r="AK103" s="6"/>
-      <c r="AL103" s="6"/>
-      <c r="AM103" s="2"/>
-      <c r="AN103" s="2"/>
-      <c r="AO103" s="2"/>
-      <c r="AP103" s="2"/>
-      <c r="AQ103" s="2"/>
-      <c r="AR103" s="2"/>
-      <c r="AS103" s="2"/>
-      <c r="AT103" s="2"/>
-      <c r="AU103" s="2"/>
-      <c r="AV103" s="2"/>
-      <c r="AW103" s="2"/>
-      <c r="AX103" s="2"/>
-      <c r="AY103" s="2"/>
-      <c r="AZ103" s="2"/>
-      <c r="BA103" s="2"/>
-      <c r="BB103" s="2"/>
-      <c r="BC103" s="2"/>
-      <c r="BD103" s="2"/>
-      <c r="BE103" s="2"/>
-      <c r="BF103" s="2"/>
-      <c r="BG103" s="2"/>
-      <c r="BH103" s="2"/>
-      <c r="BI103" s="2"/>
-      <c r="BJ103" s="2"/>
-      <c r="BK103" s="2"/>
-      <c r="BL103" s="2"/>
-      <c r="BM103" s="2"/>
-      <c r="BN103" s="2"/>
-      <c r="BO103" s="2"/>
-      <c r="BP103" s="2"/>
-    </row>
-    <row r="104" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="2"/>
-      <c r="B104" s="4"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="19"/>
-      <c r="E104" s="19"/>
-      <c r="F104" s="20"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="6"/>
-      <c r="J104" s="6"/>
-      <c r="K104" s="6"/>
-      <c r="L104" s="6"/>
-      <c r="M104" s="6"/>
-      <c r="N104" s="6"/>
-      <c r="O104" s="6"/>
-      <c r="P104" s="6"/>
-      <c r="Q104" s="6"/>
-      <c r="R104" s="6"/>
-      <c r="S104" s="6"/>
-      <c r="T104" s="6"/>
-      <c r="U104" s="6"/>
-      <c r="V104" s="6"/>
-      <c r="W104" s="6"/>
-      <c r="X104" s="6"/>
-      <c r="Y104" s="6"/>
-      <c r="Z104" s="6"/>
-      <c r="AA104" s="6"/>
-      <c r="AB104" s="6"/>
-      <c r="AC104" s="6"/>
-      <c r="AD104" s="6"/>
-      <c r="AE104" s="6"/>
-      <c r="AF104" s="6"/>
-      <c r="AG104" s="6"/>
-      <c r="AH104" s="6"/>
-      <c r="AI104" s="6"/>
-      <c r="AJ104" s="6"/>
-      <c r="AK104" s="6"/>
-      <c r="AL104" s="6"/>
-      <c r="AM104" s="2"/>
-      <c r="AN104" s="2"/>
-      <c r="AO104" s="2"/>
-      <c r="AP104" s="2"/>
-      <c r="AQ104" s="2"/>
-      <c r="AR104" s="2"/>
-      <c r="AS104" s="2"/>
-      <c r="AT104" s="2"/>
-      <c r="AU104" s="2"/>
-      <c r="AV104" s="2"/>
-      <c r="AW104" s="2"/>
-      <c r="AX104" s="2"/>
-      <c r="AY104" s="2"/>
-      <c r="AZ104" s="2"/>
-      <c r="BA104" s="2"/>
-      <c r="BB104" s="2"/>
-      <c r="BC104" s="2"/>
-      <c r="BD104" s="2"/>
-      <c r="BE104" s="2"/>
-      <c r="BF104" s="2"/>
-      <c r="BG104" s="2"/>
-      <c r="BH104" s="2"/>
-      <c r="BI104" s="2"/>
-      <c r="BJ104" s="2"/>
-      <c r="BK104" s="2"/>
-      <c r="BL104" s="2"/>
-      <c r="BM104" s="2"/>
-      <c r="BN104" s="2"/>
-      <c r="BO104" s="2"/>
-      <c r="BP104" s="2"/>
-    </row>
-    <row r="105" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="2"/>
-      <c r="B105" s="4"/>
-      <c r="C105" s="4"/>
-      <c r="D105" s="19"/>
-      <c r="E105" s="19"/>
-      <c r="F105" s="20"/>
-      <c r="H105" s="6"/>
-      <c r="I105" s="6"/>
-      <c r="J105" s="6"/>
-      <c r="K105" s="6"/>
-      <c r="L105" s="6"/>
-      <c r="M105" s="6"/>
-      <c r="N105" s="6"/>
-      <c r="O105" s="6"/>
-      <c r="P105" s="6"/>
-      <c r="Q105" s="6"/>
-      <c r="R105" s="6"/>
-      <c r="S105" s="6"/>
-      <c r="T105" s="6"/>
-      <c r="U105" s="6"/>
-      <c r="V105" s="6"/>
-      <c r="W105" s="6"/>
-      <c r="X105" s="6"/>
-      <c r="Y105" s="6"/>
-      <c r="Z105" s="6"/>
-      <c r="AA105" s="6"/>
-      <c r="AB105" s="6"/>
-      <c r="AC105" s="6"/>
-      <c r="AD105" s="6"/>
-      <c r="AE105" s="6"/>
-      <c r="AF105" s="6"/>
-      <c r="AG105" s="6"/>
-      <c r="AH105" s="6"/>
-      <c r="AI105" s="6"/>
-      <c r="AJ105" s="6"/>
-      <c r="AK105" s="6"/>
-      <c r="AL105" s="6"/>
-      <c r="AM105" s="2"/>
-      <c r="AN105" s="2"/>
-      <c r="AO105" s="2"/>
-      <c r="AP105" s="2"/>
-      <c r="AQ105" s="2"/>
-      <c r="AR105" s="2"/>
-      <c r="AS105" s="2"/>
-      <c r="AT105" s="2"/>
-      <c r="AU105" s="2"/>
-      <c r="AV105" s="2"/>
-      <c r="AW105" s="2"/>
-      <c r="AX105" s="2"/>
-      <c r="AY105" s="2"/>
-      <c r="AZ105" s="2"/>
-      <c r="BA105" s="2"/>
-      <c r="BB105" s="2"/>
-      <c r="BC105" s="2"/>
-      <c r="BD105" s="2"/>
-      <c r="BE105" s="2"/>
-      <c r="BF105" s="2"/>
-      <c r="BG105" s="2"/>
-      <c r="BH105" s="2"/>
-      <c r="BI105" s="2"/>
-      <c r="BJ105" s="2"/>
-      <c r="BK105" s="2"/>
-      <c r="BL105" s="2"/>
-      <c r="BM105" s="2"/>
-      <c r="BN105" s="2"/>
-      <c r="BO105" s="2"/>
-      <c r="BP105" s="2"/>
-    </row>
-    <row r="106" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="2"/>
-      <c r="B106" s="4"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="19"/>
-      <c r="E106" s="19"/>
-      <c r="F106" s="20"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="6"/>
-      <c r="J106" s="6"/>
-      <c r="K106" s="6"/>
-      <c r="L106" s="6"/>
-      <c r="M106" s="6"/>
-      <c r="N106" s="6"/>
-      <c r="O106" s="6"/>
-      <c r="P106" s="6"/>
-      <c r="Q106" s="6"/>
-      <c r="R106" s="6"/>
-      <c r="S106" s="6"/>
-      <c r="T106" s="6"/>
-      <c r="U106" s="6"/>
-      <c r="V106" s="6"/>
-      <c r="W106" s="6"/>
-      <c r="X106" s="6"/>
-      <c r="Y106" s="6"/>
-      <c r="Z106" s="6"/>
-      <c r="AA106" s="6"/>
-      <c r="AB106" s="6"/>
-      <c r="AC106" s="6"/>
-      <c r="AD106" s="6"/>
-      <c r="AE106" s="6"/>
-      <c r="AF106" s="6"/>
-      <c r="AG106" s="6"/>
-      <c r="AH106" s="6"/>
-      <c r="AI106" s="6"/>
-      <c r="AJ106" s="6"/>
-      <c r="AK106" s="6"/>
-      <c r="AL106" s="6"/>
-      <c r="AM106" s="2"/>
-      <c r="AN106" s="2"/>
-      <c r="AO106" s="2"/>
-      <c r="AP106" s="2"/>
-      <c r="AQ106" s="2"/>
-      <c r="AR106" s="2"/>
-      <c r="AS106" s="2"/>
-      <c r="AT106" s="2"/>
-      <c r="AU106" s="2"/>
-      <c r="AV106" s="2"/>
-      <c r="AW106" s="2"/>
-      <c r="AX106" s="2"/>
-      <c r="AY106" s="2"/>
-      <c r="AZ106" s="2"/>
-      <c r="BA106" s="2"/>
-      <c r="BB106" s="2"/>
-      <c r="BC106" s="2"/>
-      <c r="BD106" s="2"/>
-      <c r="BE106" s="2"/>
-      <c r="BF106" s="2"/>
-      <c r="BG106" s="2"/>
-      <c r="BH106" s="2"/>
-      <c r="BI106" s="2"/>
-      <c r="BJ106" s="2"/>
-      <c r="BK106" s="2"/>
-      <c r="BL106" s="2"/>
-      <c r="BM106" s="2"/>
-      <c r="BN106" s="2"/>
-      <c r="BO106" s="2"/>
-      <c r="BP106" s="2"/>
-    </row>
-    <row r="107" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="2"/>
-      <c r="B107" s="4"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="19"/>
-      <c r="E107" s="19"/>
-      <c r="F107" s="20"/>
-      <c r="H107" s="6"/>
-      <c r="I107" s="6"/>
-      <c r="J107" s="6"/>
-      <c r="K107" s="6"/>
-      <c r="L107" s="6"/>
-      <c r="M107" s="6"/>
-      <c r="N107" s="6"/>
-      <c r="O107" s="6"/>
-      <c r="P107" s="6"/>
-      <c r="Q107" s="6"/>
-      <c r="R107" s="6"/>
-      <c r="S107" s="6"/>
-      <c r="T107" s="6"/>
-      <c r="U107" s="6"/>
-      <c r="V107" s="6"/>
-      <c r="W107" s="6"/>
-      <c r="X107" s="6"/>
-      <c r="Y107" s="6"/>
-      <c r="Z107" s="6"/>
-      <c r="AA107" s="6"/>
-      <c r="AB107" s="6"/>
-      <c r="AC107" s="6"/>
-      <c r="AD107" s="6"/>
-      <c r="AE107" s="6"/>
-      <c r="AF107" s="6"/>
-      <c r="AG107" s="6"/>
-      <c r="AH107" s="6"/>
-      <c r="AI107" s="6"/>
-      <c r="AJ107" s="6"/>
-      <c r="AK107" s="6"/>
-      <c r="AL107" s="6"/>
-      <c r="AM107" s="2"/>
-      <c r="AN107" s="2"/>
-      <c r="AO107" s="2"/>
-      <c r="AP107" s="2"/>
-      <c r="AQ107" s="2"/>
-      <c r="AR107" s="2"/>
-      <c r="AS107" s="2"/>
-      <c r="AT107" s="2"/>
-      <c r="AU107" s="2"/>
-      <c r="AV107" s="2"/>
-      <c r="AW107" s="2"/>
-      <c r="AX107" s="2"/>
-      <c r="AY107" s="2"/>
-      <c r="AZ107" s="2"/>
-      <c r="BA107" s="2"/>
-      <c r="BB107" s="2"/>
-      <c r="BC107" s="2"/>
-      <c r="BD107" s="2"/>
-      <c r="BE107" s="2"/>
-      <c r="BF107" s="2"/>
-      <c r="BG107" s="2"/>
-      <c r="BH107" s="2"/>
-      <c r="BI107" s="2"/>
-      <c r="BJ107" s="2"/>
-      <c r="BK107" s="2"/>
-      <c r="BL107" s="2"/>
-      <c r="BM107" s="2"/>
-      <c r="BN107" s="2"/>
-      <c r="BO107" s="2"/>
-      <c r="BP107" s="2"/>
-    </row>
-    <row r="108" spans="1:68" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="2"/>
-      <c r="B108" s="4"/>
-      <c r="C108" s="4"/>
-      <c r="D108" s="19"/>
-      <c r="E108" s="19"/>
-      <c r="F108" s="20"/>
-      <c r="H108" s="6"/>
-      <c r="I108" s="6"/>
-      <c r="J108" s="6"/>
-      <c r="K108" s="6"/>
-      <c r="L108" s="6"/>
-      <c r="M108" s="6"/>
-      <c r="N108" s="6"/>
-      <c r="O108" s="6"/>
-      <c r="P108" s="6"/>
-      <c r="Q108" s="6"/>
-      <c r="R108" s="6"/>
-      <c r="S108" s="6"/>
-      <c r="T108" s="6"/>
-      <c r="U108" s="6"/>
-      <c r="V108" s="6"/>
-      <c r="W108" s="6"/>
-      <c r="X108" s="6"/>
-      <c r="Y108" s="6"/>
-      <c r="Z108" s="6"/>
-      <c r="AA108" s="6"/>
-      <c r="AB108" s="6"/>
-      <c r="AC108" s="6"/>
-      <c r="AD108" s="6"/>
-      <c r="AE108" s="6"/>
-      <c r="AF108" s="6"/>
-      <c r="AG108" s="6"/>
-      <c r="AH108" s="6"/>
-      <c r="AI108" s="6"/>
-      <c r="AJ108" s="6"/>
-      <c r="AK108" s="6"/>
-      <c r="AL108" s="6"/>
-      <c r="AM108" s="2"/>
-      <c r="AN108" s="2"/>
-      <c r="AO108" s="2"/>
-      <c r="AP108" s="2"/>
-      <c r="AQ108" s="2"/>
-      <c r="AR108" s="2"/>
-      <c r="AS108" s="2"/>
-      <c r="AT108" s="2"/>
-      <c r="AU108" s="2"/>
-      <c r="AV108" s="2"/>
-      <c r="AW108" s="2"/>
-      <c r="AX108" s="2"/>
-      <c r="AY108" s="2"/>
-      <c r="AZ108" s="2"/>
-      <c r="BA108" s="2"/>
-      <c r="BB108" s="2"/>
-      <c r="BC108" s="2"/>
-      <c r="BD108" s="2"/>
-      <c r="BE108" s="2"/>
-      <c r="BF108" s="2"/>
-      <c r="BG108" s="2"/>
-      <c r="BH108" s="2"/>
-      <c r="BI108" s="2"/>
-      <c r="BJ108" s="2"/>
-      <c r="BK108" s="2"/>
-      <c r="BL108" s="2"/>
-      <c r="BM108" s="2"/>
-      <c r="BN108" s="2"/>
-      <c r="BO108" s="2"/>
-      <c r="BP108" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
@@ -8885,23 +6465,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="27">
+      <c r="A1" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="18">
         <v>20262112234</v>
       </c>
-      <c r="C1" s="27" t="s">
-        <v>10</v>
+      <c r="C1" s="18" t="s">
+        <v>12</v>
       </c>
       <c r="D1" s="8">
         <v>19673.87</v>
       </c>
-      <c r="E1" s="22">
+      <c r="E1" s="15">
         <f>+D1*0.21</f>
         <v>4131.5126999999993</v>
       </c>
-      <c r="F1" s="23">
+      <c r="F1" s="16">
         <f>+E1+D1</f>
         <v>23805.382699999998</v>
       </c>
@@ -8910,23 +6490,23 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="27">
+      <c r="A2" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="18">
         <v>20262112234</v>
       </c>
-      <c r="C2" s="27" t="s">
-        <v>10</v>
+      <c r="C2" s="18" t="s">
+        <v>12</v>
       </c>
       <c r="D2" s="8">
         <v>124535.1</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="15">
         <f>+D2*0.21</f>
         <v>26152.370999999999</v>
       </c>
-      <c r="F2" s="23">
+      <c r="F2" s="16">
         <f>+E2+D2</f>
         <v>150687.47100000002</v>
       </c>
